--- a/output/yearly_surface_area_iteration_81_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_81_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497614911389</v>
+        <v>10.84497616665423</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907130389766</v>
+        <v>37.78907136501655</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.324819621385452</v>
+        <v>6.116288197457628</v>
       </c>
       <c r="C2" t="n">
-        <v>8.416523068507905</v>
+        <v>7.191301933607885</v>
       </c>
       <c r="D2" t="n">
-        <v>25.70510014029423</v>
+        <v>26.40803149653495</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.67698930976957</v>
+        <v>20.00801821255</v>
       </c>
       <c r="C3" t="n">
-        <v>28.14670668075605</v>
+        <v>23.85156047467626</v>
       </c>
       <c r="D3" t="n">
-        <v>78.5938124634784</v>
+        <v>87.184104875638</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.43680527959437</v>
+        <v>39.1815508764902</v>
       </c>
       <c r="C4" t="n">
-        <v>83.27674901273569</v>
+        <v>54.63720498444773</v>
       </c>
       <c r="D4" t="n">
-        <v>101.9868967602714</v>
+        <v>93.98467122295565</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.45554060143309</v>
+        <v>49.03829782712819</v>
       </c>
       <c r="C5" t="n">
-        <v>129.9588523496716</v>
+        <v>95.91675070491338</v>
       </c>
       <c r="D5" t="n">
-        <v>77.45989386507335</v>
+        <v>61.5801247488812</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.75104666041137</v>
+        <v>48.98626519880311</v>
       </c>
       <c r="C6" t="n">
-        <v>161.8921599257075</v>
+        <v>107.5524244956466</v>
       </c>
       <c r="D6" t="n">
-        <v>50.636583089642</v>
+        <v>42.62650357069227</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.39298648580176</v>
+        <v>36.17151241526948</v>
       </c>
       <c r="C7" t="n">
-        <v>153.2498348852228</v>
+        <v>104.801567428347</v>
       </c>
       <c r="D7" t="n">
-        <v>39.94436884268997</v>
+        <v>38.32743037379547</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.19178495969339</v>
+        <v>19.02627050830318</v>
       </c>
       <c r="C8" t="n">
-        <v>100.0548172783137</v>
+        <v>71.8492057353028</v>
       </c>
       <c r="D8" t="n">
-        <v>35.549084370777</v>
+        <v>36.04977569994287</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>8.653124265231384</v>
       </c>
       <c r="C9" t="n">
-        <v>48.59062087399162</v>
+        <v>41.3796839862988</v>
       </c>
       <c r="D9" t="n">
-        <v>33.72499713628642</v>
+        <v>34.39062207976576</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>34.44952694202058</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>28.60910984945629</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>26.90381408717959</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>24.71549845441346</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>18.18589447346791</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.616814984346772</v>
+        <v>7.685800131558699</v>
       </c>
       <c r="C21" t="n">
-        <v>91.40177981216127</v>
+        <v>93.19032659514922</v>
       </c>
       <c r="D21" t="n">
-        <v>7.616814984346772</v>
+        <v>8.646525148003535</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.122980504938109</v>
+        <v>9.95688521647115</v>
       </c>
       <c r="C2" t="n">
-        <v>6.620906517440489</v>
+        <v>11.98124898262807</v>
       </c>
       <c r="D2" t="n">
-        <v>23.99096864867931</v>
+        <v>24.72237068834318</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.58019719767664</v>
+        <v>20.16018910670825</v>
       </c>
       <c r="C3" t="n">
-        <v>30.07584091960103</v>
+        <v>25.82978209873358</v>
       </c>
       <c r="D3" t="n">
-        <v>79.82590583230815</v>
+        <v>87.42463306317848</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.41127983928396</v>
+        <v>38.63275390981624</v>
       </c>
       <c r="C4" t="n">
-        <v>76.28277836768142</v>
+        <v>56.5133248472634</v>
       </c>
       <c r="D4" t="n">
-        <v>114.5964642736174</v>
+        <v>112.7713952914226</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.13709449235862</v>
+        <v>53.30890034060182</v>
       </c>
       <c r="C5" t="n">
-        <v>140.2917469368692</v>
+        <v>98.2238578098934</v>
       </c>
       <c r="D5" t="n">
-        <v>91.4497986505904</v>
+        <v>77.41080647986101</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.83533809425636</v>
+        <v>57.03659637362695</v>
       </c>
       <c r="C6" t="n">
-        <v>179.9651534131871</v>
+        <v>127.8795107120768</v>
       </c>
       <c r="D6" t="n">
-        <v>60.94100699341652</v>
+        <v>50.99884799250906</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>45.8132566186774</v>
+        <v>46.95110220789945</v>
       </c>
       <c r="C7" t="n">
-        <v>187.7445222216388</v>
+        <v>129.594623951396</v>
       </c>
       <c r="D7" t="n">
-        <v>43.95677170994669</v>
+        <v>41.20198765183014</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.45319189093031</v>
+        <v>28.12216298814988</v>
       </c>
       <c r="C8" t="n">
-        <v>145.5342796775471</v>
+        <v>103.0589652533089</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.21943812632832</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.42499894494763</v>
+        <v>13.42343636016663</v>
       </c>
       <c r="C9" t="n">
-        <v>80.31874317984003</v>
+        <v>64.12186955517615</v>
       </c>
       <c r="D9" t="n">
-        <v>34.72343455150543</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>6.975317438673588</v>
       </c>
       <c r="C10" t="n">
-        <v>42.70602513473626</v>
+        <v>39.57424995818893</v>
       </c>
       <c r="D10" t="n">
-        <v>35.16129402759952</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>31.8076438698924</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>30.37527396939631</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.0569667290421</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>24.58296251434014</v>
+        <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1307,7 +1307,7 @@
         <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.779995194877726</v>
+        <v>7.86689983420503</v>
       </c>
       <c r="C21" t="n">
-        <v>99.19493873469101</v>
+        <v>101.2863353653898</v>
       </c>
       <c r="D21" t="n">
-        <v>8.752494594237442</v>
+        <v>9.833624792756288</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10.38001847700153</v>
+        <v>10.10905611062941</v>
       </c>
       <c r="C2" t="n">
-        <v>11.13596420927157</v>
+        <v>13.22021458538755</v>
       </c>
       <c r="D2" t="n">
-        <v>31.31382477465626</v>
+        <v>28.99395494952105</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.87610416728243</v>
+        <v>25.78069471352124</v>
       </c>
       <c r="C3" t="n">
-        <v>27.86690858504571</v>
+        <v>35.43127464626738</v>
       </c>
       <c r="D3" t="n">
-        <v>79.33503198018475</v>
+        <v>86.3201668959008</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.66653424238812</v>
+        <v>37.70107533848601</v>
       </c>
       <c r="C4" t="n">
-        <v>75.46596427774806</v>
+        <v>60.03583561010095</v>
       </c>
       <c r="D4" t="n">
-        <v>122.4965880496915</v>
+        <v>126.9252519435489</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.83060928218437</v>
+        <v>54.92878405260905</v>
       </c>
       <c r="C5" t="n">
-        <v>138.4755136840126</v>
+        <v>99.64739198105129</v>
       </c>
       <c r="D5" t="n">
-        <v>105.9796646734432</v>
+        <v>94.39504176333082</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>62.792583163626</v>
+        <v>63.31585468998956</v>
       </c>
       <c r="C6" t="n">
-        <v>195.462040924723</v>
+        <v>139.1499743568302</v>
       </c>
       <c r="D6" t="n">
-        <v>70.64165605907925</v>
+        <v>61.26302024040947</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>53.83806235319084</v>
+        <v>56.47307319138927</v>
       </c>
       <c r="C7" t="n">
-        <v>215.5917958525995</v>
+        <v>154.507453694363</v>
       </c>
       <c r="D7" t="n">
-        <v>49.40645321622073</v>
+        <v>45.09461729916874</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>35.04839304161113</v>
+        <v>37.55184968744049</v>
       </c>
       <c r="C8" t="n">
-        <v>187.5089027726195</v>
+        <v>132.3494080095125</v>
       </c>
       <c r="D8" t="n">
-        <v>39.80496066868692</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.63906100220244</v>
+        <v>19.52499834206056</v>
       </c>
       <c r="C9" t="n">
-        <v>118.2593649581622</v>
+        <v>91.30155474724909</v>
       </c>
       <c r="D9" t="n">
-        <v>35.83280945730432</v>
+        <v>36.72030938194344</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.541205026947251</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>62.35079669671494</v>
+        <v>55.37547925804135</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>5.686282702997524</v>
       </c>
       <c r="C11" t="n">
         <v>38.38240824523329</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>36.45032876327558</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.13827186204534</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>26.42668470291564</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.65056423721292</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1598,10 +1598,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.927329969325692</v>
+        <v>8.032597705566523</v>
       </c>
       <c r="C21" t="n">
-        <v>106.0280383397311</v>
+        <v>109.4441437383439</v>
       </c>
       <c r="D21" t="n">
-        <v>9.909162461657115</v>
+        <v>11.04482184515397</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.492518552362409</v>
+        <v>9.196030745679874</v>
       </c>
       <c r="C2" t="n">
-        <v>7.928594459497242</v>
+        <v>8.988881980083795</v>
       </c>
       <c r="D2" t="n">
-        <v>25.96428153421539</v>
+        <v>23.85745096090174</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.43984833369835</v>
+        <v>28.82411259668635</v>
       </c>
       <c r="C3" t="n">
-        <v>44.46826226385928</v>
+        <v>51.25213890020474</v>
       </c>
       <c r="D3" t="n">
-        <v>86.51651643675017</v>
+        <v>94.54721265748907</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.34225440035042</v>
+        <v>26.38054256081604</v>
       </c>
       <c r="C4" t="n">
-        <v>108.2406296363236</v>
+        <v>83.16188453133881</v>
       </c>
       <c r="D4" t="n">
-        <v>117.4042627077633</v>
+        <v>116.7788894201581</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.36746104549135</v>
+        <v>35.66198535676539</v>
       </c>
       <c r="C5" t="n">
-        <v>116.7788894201581</v>
+        <v>83.12948685709868</v>
       </c>
       <c r="D5" t="n">
-        <v>69.67954330891737</v>
+        <v>61.97282383057992</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.40887437551896</v>
+        <v>35.05919226635785</v>
       </c>
       <c r="C6" t="n">
-        <v>142.0078419238926</v>
+        <v>101.7561860497734</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>29.66547037922588</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.2360046641135</v>
+        <v>24.852943133008</v>
       </c>
       <c r="C7" t="n">
-        <v>131.8703151298401</v>
+        <v>93.06379187637214</v>
       </c>
       <c r="D7" t="n">
-        <v>27.96704685087888</v>
+        <v>28.38625312059227</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.18348900970292</v>
+        <v>13.51866588747858</v>
       </c>
       <c r="C8" t="n">
-        <v>87.12029127486194</v>
+        <v>67.25953521794897</v>
       </c>
       <c r="D8" t="n">
-        <v>26.36974333606933</v>
+        <v>27.03733177495716</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>47.59218345877262</v>
+        <v>42.26718391093791</v>
       </c>
       <c r="D9" t="n">
-        <v>27.29062268265283</v>
+        <v>27.73437264497238</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
         <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>27.90126975469435</v>
+        <v>28.75539025738908</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.843141351498762</v>
+        <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>25.76596849795753</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>28.25371718051895</v>
+        <v>29.14219885286231</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>23.64932044760141</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>26.03594911662541</v>
+        <v>26.68684784454105</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>23.96838845148163</v>
+        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1895,10 +1895,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3583379120500857</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
         <v>22.57528845915541</v>
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>71.95719798276996</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.633268326968198</v>
+        <v>5.428083056780614</v>
       </c>
       <c r="C2" t="n">
-        <v>3.688426124855267</v>
+        <v>3.835688280492288</v>
       </c>
       <c r="D2" t="n">
-        <v>18.00917988670349</v>
+        <v>16.46096375710627</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>30.32127784566274</v>
+        <v>30.92014394525329</v>
       </c>
       <c r="C3" t="n">
-        <v>38.58759351542088</v>
+        <v>44.28173020005238</v>
       </c>
       <c r="D3" t="n">
-        <v>87.2135573067654</v>
+        <v>92.46590752448583</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.73110860669016</v>
+        <v>38.55617758888499</v>
       </c>
       <c r="C4" t="n">
-        <v>113.3967685790278</v>
+        <v>106.9005440200267</v>
       </c>
       <c r="D4" t="n">
-        <v>131.5708820800448</v>
+        <v>135.2848336452105</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.99992755120455</v>
+        <v>39.46625771072178</v>
       </c>
       <c r="C5" t="n">
-        <v>155.0425061931776</v>
+        <v>117.0734137314322</v>
       </c>
       <c r="D5" t="n">
-        <v>86.86012813323656</v>
+        <v>81.55869053030378</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.60133798328035</v>
+        <v>41.09694064747573</v>
       </c>
       <c r="C6" t="n">
-        <v>165.0317890838888</v>
+        <v>118.9033914521482</v>
       </c>
       <c r="D6" t="n">
-        <v>40.13090090649688</v>
+        <v>37.07177506006381</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.55917958525995</v>
+        <v>23.47555110394973</v>
       </c>
       <c r="C7" t="n">
-        <v>162.8915790886308</v>
+        <v>117.1980956898715</v>
       </c>
       <c r="D7" t="n">
-        <v>30.66194429903638</v>
+        <v>30.84160412891355</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.846929473595507</v>
+        <v>11.09865779651019</v>
       </c>
       <c r="C8" t="n">
-        <v>113.2396889463483</v>
+        <v>87.7044311588888</v>
       </c>
       <c r="D8" t="n">
-        <v>27.12078032981814</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.659374604355361</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>49.92187076095029</v>
+        <v>47.48124596819272</v>
       </c>
       <c r="D9" t="n">
-        <v>28.06718511671205</v>
+        <v>28.73281006019139</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.992947839621025</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.02951885105219</v>
+        <v>32.74128593663113</v>
       </c>
       <c r="D10" t="n">
-        <v>29.18245050873644</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>28.25371718051895</v>
+        <v>29.67528785626833</v>
       </c>
       <c r="D11" t="n">
-        <v>28.78680618392497</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>19.52696183746906</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
-        <v>27.55471281509523</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2181,7 +2181,7 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
         <v>25.23582473766426</v>
@@ -2192,10 +2192,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
         <v>18.74450891718435</v>
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>62.58837964114266</v>
+        <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.347579745032376</v>
+        <v>5.966080798707867</v>
       </c>
       <c r="C2" t="n">
-        <v>7.248243300454201</v>
+        <v>5.527239574909543</v>
       </c>
       <c r="D2" t="n">
-        <v>13.85344185462674</v>
+        <v>16.09575361112646</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.76949457814703</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="C3" t="n">
-        <v>26.11939767148639</v>
+        <v>28.80447764260142</v>
       </c>
       <c r="D3" t="n">
-        <v>82.57479940419923</v>
+        <v>85.52495125546089</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.90750439828511</v>
+        <v>48.11545498513618</v>
       </c>
       <c r="C4" t="n">
-        <v>105.9688654486965</v>
+        <v>108.7000875619111</v>
       </c>
       <c r="D4" t="n">
-        <v>142.1894652491783</v>
+        <v>148.3283336438336</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.04396732917541</v>
+        <v>47.95837535245669</v>
       </c>
       <c r="C5" t="n">
-        <v>179.6352861845602</v>
+        <v>156.2696908234861</v>
       </c>
       <c r="D5" t="n">
-        <v>107.3050240741764</v>
+        <v>106.4950822181728</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.04160292313942</v>
+        <v>46.93343074922303</v>
       </c>
       <c r="C6" t="n">
-        <v>201.1777760588479</v>
+        <v>151.8694976130519</v>
       </c>
       <c r="D6" t="n">
-        <v>54.29948377418685</v>
+        <v>50.47557646614552</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.42239785920016</v>
+        <v>34.01559445674349</v>
       </c>
       <c r="C7" t="n">
-        <v>198.4043387943506</v>
+        <v>144.0272969515283</v>
       </c>
       <c r="D7" t="n">
-        <v>34.61446055633404</v>
+        <v>33.83593462686632</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.43659999094934</v>
+        <v>16.43936530761284</v>
       </c>
       <c r="C8" t="n">
-        <v>157.7177686872501</v>
+        <v>118.8307421220339</v>
       </c>
       <c r="D8" t="n">
-        <v>28.62285431731576</v>
+        <v>29.79113408536946</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.212499472473814</v>
+        <v>7.21093688769282</v>
       </c>
       <c r="C9" t="n">
-        <v>85.86561770883451</v>
+        <v>73.66249374504666</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>29.39843500367073</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.562361508084175</v>
+        <v>2.847068342315751</v>
       </c>
       <c r="C10" t="n">
         <v>42.99073196896783</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>30.7483380970101</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>31.98534020436108</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>23.64932044760141</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>27.98864530037232</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.95125677215293</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
         <v>19.35908298004286</v>
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.0501923061036</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>33.70830742531424</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.09962384868121</v>
+        <v>34.9050578767911</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.254493639578176</v>
+        <v>3.548036203147973</v>
       </c>
       <c r="C2" t="n">
-        <v>3.534291735288517</v>
+        <v>2.580032966760618</v>
       </c>
       <c r="D2" t="n">
-        <v>9.681995859282043</v>
+        <v>11.27831762638736</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.55351008321273</v>
+        <v>25.14746744428205</v>
       </c>
       <c r="C3" t="n">
-        <v>28.64739800992193</v>
+        <v>27.5331143656018</v>
       </c>
       <c r="D3" t="n">
-        <v>80.13024762062467</v>
+        <v>83.08039947188632</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.00433756810704</v>
+        <v>53.30988208830605</v>
       </c>
       <c r="C4" t="n">
-        <v>103.2631687757923</v>
+        <v>105.8284755269892</v>
       </c>
       <c r="D4" t="n">
-        <v>151.3275728803076</v>
+        <v>157.8620855997744</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.88474427463818</v>
+        <v>50.24093876483053</v>
       </c>
       <c r="C5" t="n">
-        <v>214.0455432184109</v>
+        <v>191.1953654020664</v>
       </c>
       <c r="D5" t="n">
-        <v>110.0784613386736</v>
+        <v>112.72918014014</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.34724525432967</v>
+        <v>40.17115256237099</v>
       </c>
       <c r="C6" t="n">
-        <v>235.5929418312199</v>
+        <v>184.0305706564731</v>
       </c>
       <c r="D6" t="n">
-        <v>52.48815925985148</v>
+        <v>49.59004003691489</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>10.89936301254809</v>
       </c>
       <c r="C7" t="n">
-        <v>205.1116391097649</v>
+        <v>153.6091545449772</v>
       </c>
       <c r="D7" t="n">
-        <v>34.2551408965797</v>
+        <v>34.07548106670254</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.255876297909922</v>
+        <v>5.006913291658733</v>
       </c>
       <c r="C8" t="n">
-        <v>108.0658785449676</v>
+        <v>90.37478491444013</v>
       </c>
       <c r="D8" t="n">
-        <v>30.62561963397925</v>
+        <v>31.46010518258904</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
         <v>32.72655972106742</v>
       </c>
       <c r="D9" t="n">
-        <v>30.84062238120929</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.0542014123786</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>22.91890015564179</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>18.8358114536793</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>22.38973814305275</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.53673825678252</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.59876828859932</v>
+        <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>29.96293993361265</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.022220344299182</v>
+        <v>4.067380738694535</v>
       </c>
       <c r="C2" t="n">
-        <v>10.28380720198534</v>
+        <v>5.341689258806895</v>
       </c>
       <c r="D2" t="n">
-        <v>13.83871563906304</v>
+        <v>12.89918308609884</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.25559856046944</v>
+        <v>18.8839170911874</v>
       </c>
       <c r="C3" t="n">
-        <v>21.35792130588936</v>
+        <v>18.6384801651257</v>
       </c>
       <c r="D3" t="n">
-        <v>70.81346190732243</v>
+        <v>74.66191290796993</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.24308218668826</v>
+        <v>50.78286349757476</v>
       </c>
       <c r="C4" t="n">
-        <v>88.12658267171493</v>
+        <v>87.51397210426492</v>
       </c>
       <c r="D4" t="n">
-        <v>155.4754569307504</v>
+        <v>161.9844442099067</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.80668748438396</v>
+        <v>63.00365892003907</v>
       </c>
       <c r="C5" t="n">
-        <v>204.9643769541279</v>
+        <v>194.606938674324</v>
       </c>
       <c r="D5" t="n">
-        <v>132.7813769993811</v>
+        <v>136.7819988941869</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.93343074922303</v>
+        <v>51.44161620712438</v>
       </c>
       <c r="C6" t="n">
-        <v>282.3653659569464</v>
+        <v>238.8533259570235</v>
       </c>
       <c r="D6" t="n">
-        <v>69.51460969460392</v>
+        <v>67.09951034215676</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.52303484665207</v>
+        <v>22.81679839440012</v>
       </c>
       <c r="C7" t="n">
-        <v>264.5790427991069</v>
+        <v>204.8122060599696</v>
       </c>
       <c r="D7" t="n">
-        <v>39.04606969330414</v>
+        <v>39.1059563032632</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.841398840268521</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="C8" t="n">
-        <v>171.0695374650067</v>
+        <v>136.9390785268664</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>33.12907627980861</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>67.33905678199295</v>
+        <v>61.90311974357836</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>24.20008090968388</v>
+        <v>24.76949457814703</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>22.21204180858408</v>
+        <v>23.81130881880213</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.70640068316797</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.82929907264807</v>
+        <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
         <v>11.82515109765283</v>
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.1456838753228</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>33.99988649347554</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.864739800992193</v>
+        <v>3.027709919897163</v>
       </c>
       <c r="C2" t="n">
-        <v>5.751078051477815</v>
+        <v>3.351686662298611</v>
       </c>
       <c r="D2" t="n">
-        <v>10.42419712369263</v>
+        <v>9.612291772280519</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.50317890838888</v>
+        <v>16.95478285234242</v>
       </c>
       <c r="C3" t="n">
-        <v>29.57514959043516</v>
+        <v>19.98838325846506</v>
       </c>
       <c r="D3" t="n">
-        <v>66.89137982885642</v>
+        <v>69.38011025912209</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.78889285252048</v>
+        <v>46.29038600294135</v>
       </c>
       <c r="C4" t="n">
-        <v>76.30830380799182</v>
+        <v>72.46672504127406</v>
       </c>
       <c r="D4" t="n">
-        <v>155.8072876547858</v>
+        <v>164.4859373603276</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>64.94261063592651</v>
+        <v>68.94323253073227</v>
       </c>
       <c r="C5" t="n">
-        <v>194.6560260595364</v>
+        <v>186.8020444255619</v>
       </c>
       <c r="D5" t="n">
-        <v>148.8329519638165</v>
+        <v>152.367243699105</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.37998708593508</v>
+        <v>61.06176196103888</v>
       </c>
       <c r="C6" t="n">
-        <v>309.8572469189698</v>
+        <v>273.5905049763884</v>
       </c>
       <c r="D6" t="n">
-        <v>81.4290998333432</v>
+        <v>81.8316163920844</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.30723027816702</v>
+        <v>20.60099382591507</v>
       </c>
       <c r="C7" t="n">
-        <v>317.63857922283</v>
+        <v>255.6559379152077</v>
       </c>
       <c r="D7" t="n">
-        <v>43.59745205019235</v>
+        <v>43.47767883027424</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.673119072214817</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>216.1317570899353</v>
+        <v>174.4909282143068</v>
       </c>
       <c r="D8" t="n">
-        <v>33.62976760897448</v>
+        <v>34.13045893814036</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>74.2171811979461</v>
+        <v>71.77655640518853</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>30.32127784566274</v>
+        <v>32.31422568528377</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>21.67895280517806</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>23.45591614986479</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.05550195525234</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>19.52696183746906</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>10.926851948267</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
         <v>11.06233313145306</v>
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.271584261177872</v>
+        <v>5.67548347825081</v>
       </c>
       <c r="C2" t="n">
-        <v>18.25559856046944</v>
+        <v>9.021279654323941</v>
       </c>
       <c r="D2" t="n">
-        <v>13.1750541909922</v>
+        <v>11.22333975494954</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.28795517698058</v>
+        <v>13.72483290537041</v>
       </c>
       <c r="C3" t="n">
-        <v>26.12921514852886</v>
+        <v>16.77806826557799</v>
       </c>
       <c r="D3" t="n">
-        <v>61.05979846563037</v>
+        <v>62.38024912784233</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.79041437957247</v>
+        <v>39.93455136564751</v>
       </c>
       <c r="C4" t="n">
-        <v>74.95545547153972</v>
+        <v>62.29483707757286</v>
       </c>
       <c r="D4" t="n">
-        <v>153.4972353066931</v>
+        <v>161.7674779672682</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>65.55620295108078</v>
+        <v>68.96777622333845</v>
       </c>
       <c r="C5" t="n">
-        <v>172.1985473248906</v>
+        <v>163.7800607609742</v>
       </c>
       <c r="D5" t="n">
-        <v>161.6938468894497</v>
+        <v>169.7687217568797</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>65.20768251607315</v>
+        <v>72.97625209977816</v>
       </c>
       <c r="C6" t="n">
-        <v>310.7830350040746</v>
+        <v>283.8546772242889</v>
       </c>
       <c r="D6" t="n">
-        <v>100.6693913411722</v>
+        <v>101.7561860497734</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.45854259780804</v>
+        <v>37.72856427420492</v>
       </c>
       <c r="C7" t="n">
-        <v>368.0631048083547</v>
+        <v>311.8894646667607</v>
       </c>
       <c r="D7" t="n">
-        <v>52.22112388429633</v>
+        <v>51.80191761458295</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.511752595819845</v>
+        <v>10.59796646734432</v>
       </c>
       <c r="C8" t="n">
-        <v>293.5720160009237</v>
+        <v>240.2483894447582</v>
       </c>
       <c r="D8" t="n">
-        <v>36.13322425480386</v>
+        <v>37.21805546799658</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>138.8937382060217</v>
+        <v>124.2499894494763</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>33.50312215512664</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>48.9695754878309</v>
+        <v>50.1084028247572</v>
       </c>
       <c r="D10" t="n">
-        <v>26.1930287493049</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>27.8983245115816</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>24.87748682561417</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.48783079801943</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.91060420565131</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>11.67690719431156</v>
+      </c>
+      <c r="D14" t="n">
         <v>11.36962016288231</v>
-      </c>
-      <c r="D14" t="n">
-        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.45221014322606</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.618182258506002</v>
+        <v>8.118071766416875</v>
       </c>
       <c r="C2" t="n">
-        <v>11.26064616771091</v>
+        <v>7.674321804097318</v>
       </c>
       <c r="D2" t="n">
-        <v>15.45172711714055</v>
+        <v>6.949791998363171</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.122939447209104</v>
+        <v>4.058545009356314</v>
       </c>
       <c r="C2" t="n">
-        <v>10.80707872834889</v>
+        <v>5.196390598578367</v>
       </c>
       <c r="D2" t="n">
-        <v>9.801769079200154</v>
+        <v>8.260425183532663</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.80890335503714</v>
+        <v>19.15880644837651</v>
       </c>
       <c r="C3" t="n">
-        <v>42.3378697456437</v>
+        <v>24.59768872990384</v>
       </c>
       <c r="D3" t="n">
-        <v>66.83738370512286</v>
+        <v>67.65714303816894</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.48932093400496</v>
+        <v>53.23330576737479</v>
       </c>
       <c r="C4" t="n">
-        <v>106.5304251355256</v>
+        <v>90.95990654617123</v>
       </c>
       <c r="D4" t="n">
-        <v>155.7434740540097</v>
+        <v>165.609056733986</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.33095645398497</v>
+        <v>43.02509313861647</v>
       </c>
       <c r="C5" t="n">
-        <v>259.7213551584937</v>
+        <v>241.019061392592</v>
       </c>
       <c r="D5" t="n">
-        <v>147.0903497887784</v>
+        <v>152.6126806251667</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.12582793705961</v>
+        <v>23.42646371873739</v>
       </c>
       <c r="C6" t="n">
-        <v>297.2584786303705</v>
+        <v>261.0722399995374</v>
       </c>
       <c r="D6" t="n">
-        <v>78.57123226628075</v>
+        <v>79.5372720072596</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.629341336151211</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>206.4291445288641</v>
+        <v>168.9401266944954</v>
       </c>
       <c r="D7" t="n">
-        <v>31.50035683846316</v>
+        <v>32.75797564760332</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>2.002765316663493</v>
       </c>
       <c r="C8" t="n">
-        <v>102.3079282595601</v>
+        <v>91.54306468249383</v>
       </c>
       <c r="D8" t="n">
-        <v>23.699389580518</v>
+        <v>24.61732368398877</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>37.38593432542277</v>
+        <v>38.162496759482</v>
       </c>
       <c r="D9" t="n">
-        <v>19.96874830438012</v>
+        <v>20.1906232855399</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.4988920646734</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>18.50594422505238</v>
+        <v>19.50241814486289</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>14.74879576089983</v>
+        <v>15.81497376771187</v>
       </c>
       <c r="D11" t="n">
-        <v>15.99267010218054</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.19741340401162</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>9.626036240139976</v>
+      </c>
+      <c r="D13" t="n">
         <v>9.365873098514571</v>
-      </c>
-      <c r="D13" t="n">
-        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.166177403924969</v>
+        <v>7.558475574996192</v>
       </c>
       <c r="C2" t="n">
-        <v>11.87423848286517</v>
+        <v>3.80132711084365</v>
       </c>
       <c r="D2" t="n">
-        <v>28.20070280448963</v>
+        <v>12.63509295365645</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.41544350981242</v>
+        <v>17.23458094805276</v>
       </c>
       <c r="C3" t="n">
-        <v>28.37250865273282</v>
+        <v>19.33552103514093</v>
       </c>
       <c r="D3" t="n">
-        <v>16.11538856521139</v>
+        <v>8.973174016815847</v>
       </c>
     </row>
     <row r="4">
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
-        <v>18.43525839034661</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4585,10 +4585,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>20.72076704583318</v>
+        <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
       </c>
       <c r="D9" t="n">
-        <v>39.60468413702056</v>
+        <v>39.2718716652809</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>50.67781649322036</v>
       </c>
     </row>
     <row r="11">
@@ -4638,7 +4638,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.930157044278233</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
         <v>27.36523550817559</v>
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>26.15866757965626</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39577133822607</v>
+        <v>13.39809768923389</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13080288836004</v>
+        <v>70.14298202010684</v>
       </c>
       <c r="D21" t="n">
-        <v>1.575973098614832</v>
+        <v>1.576246786968693</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.461462478725005</v>
+        <v>5.62345084992573</v>
       </c>
       <c r="C2" t="n">
-        <v>6.507023783747859</v>
+        <v>7.760715602071037</v>
       </c>
       <c r="D2" t="n">
-        <v>26.04871183678062</v>
+        <v>13.59818745152257</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.0247489812512</v>
+        <v>22.60964962880404</v>
       </c>
       <c r="C3" t="n">
-        <v>39.39262663290327</v>
+        <v>16.51299638543135</v>
       </c>
       <c r="D3" t="n">
-        <v>34.93549205562275</v>
+        <v>17.41620427333842</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.04947260030661</v>
+        <v>19.89708072197011</v>
       </c>
       <c r="C4" t="n">
-        <v>43.07418052382881</v>
+        <v>30.00515508489526</v>
       </c>
       <c r="D4" t="n">
-        <v>23.11328620108265</v>
+        <v>19.76945352041802</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.117048960983624</v>
+        <v>3.043417883165113</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.424156065963628</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.58368222013712</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4910,10 +4910,10 @@
         <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>25.36836067773758</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.96770980341364</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4924,10 +4924,10 @@
         <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>40.04843409934012</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>50.1084028247572</v>
       </c>
     </row>
     <row r="11">
@@ -4955,7 +4955,7 @@
         <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>48.33340297547896</v>
+        <v>47.97801030654161</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.292021036517808</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>44.2611134982632</v>
+        <v>44.69504598354028</v>
       </c>
     </row>
     <row r="13">
@@ -4994,7 +4994,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
         <v>44.86390658867074</v>
@@ -5025,7 +5025,7 @@
         <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43035086827265</v>
+        <v>15.44108895379843</v>
       </c>
       <c r="C21" t="n">
-        <v>86.0851153703632</v>
+        <v>86.14502258434915</v>
       </c>
       <c r="D21" t="n">
-        <v>3.248494919636347</v>
+        <v>3.250755569220722</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.447137173788803</v>
+        <v>5.774639996379739</v>
       </c>
       <c r="C2" t="n">
-        <v>8.990845475492289</v>
+        <v>4.559236338522187</v>
       </c>
       <c r="D2" t="n">
-        <v>24.59179824367835</v>
+        <v>24.55056484009999</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.56899706230243</v>
+        <v>20.84250376115979</v>
       </c>
       <c r="C3" t="n">
-        <v>31.09685853201772</v>
+        <v>24.81367322483813</v>
       </c>
       <c r="D3" t="n">
-        <v>46.96190143264618</v>
+        <v>24.25407703341745</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.20332925243288</v>
+        <v>33.3489877655599</v>
       </c>
       <c r="C4" t="n">
-        <v>74.22798042269284</v>
+        <v>36.69282044622454</v>
       </c>
       <c r="D4" t="n">
-        <v>34.53592073999429</v>
+        <v>24.05772749256809</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>18.94773069196344</v>
+        <v>17.15604113171301</v>
       </c>
       <c r="C5" t="n">
-        <v>46.95208395560371</v>
+        <v>33.89483948912113</v>
       </c>
       <c r="D5" t="n">
-        <v>31.24412068765475</v>
+        <v>29.550605897829</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.997496725243765</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.47801332097696</v>
+        <v>12.11574841810989</v>
       </c>
       <c r="D6" t="n">
-        <v>36.10573531908495</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.19419042345839</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.46978379091126</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.873436661610169</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>40.60312155223957</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
-        <v>49.39663573917827</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.09685853201771</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
-        <v>49.22188464782232</v>
+        <v>49.75497365122833</v>
       </c>
     </row>
     <row r="12">
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5291,10 +5291,10 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>45.00822350119503</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5322,7 +5322,7 @@
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5364,7 +5364,7 @@
         <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>31.56809743005619</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.7094028137111</v>
+        <v>16.73496335148302</v>
       </c>
       <c r="C21" t="n">
-        <v>101.0918870229521</v>
+        <v>102.0832764440464</v>
       </c>
       <c r="D21" t="n">
-        <v>4.177350703427774</v>
+        <v>5.020489005444907</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.794274950464675</v>
+        <v>5.713771638716436</v>
       </c>
       <c r="C2" t="n">
-        <v>6.478553100324701</v>
+        <v>5.034402227377644</v>
       </c>
       <c r="D2" t="n">
-        <v>22.96013355922015</v>
+        <v>31.32364225169873</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.71135047941821</v>
+        <v>20.26327261565417</v>
       </c>
       <c r="C3" t="n">
-        <v>33.14871123389355</v>
+        <v>20.69033286700153</v>
       </c>
       <c r="D3" t="n">
-        <v>54.67352964950487</v>
+        <v>37.51748851779185</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.24536447726624</v>
+        <v>37.31819373382976</v>
       </c>
       <c r="C4" t="n">
-        <v>76.1168630056637</v>
+        <v>50.88496525881643</v>
       </c>
       <c r="D4" t="n">
-        <v>48.28137034715389</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.96280106489242</v>
+        <v>33.45305302221007</v>
       </c>
       <c r="C5" t="n">
-        <v>93.3396629812655</v>
+        <v>51.86082247683777</v>
       </c>
       <c r="D5" t="n">
-        <v>36.34920874973816</v>
+        <v>31.24412068765475</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.29562923216531</v>
+        <v>14.61135108230528</v>
       </c>
       <c r="C6" t="n">
-        <v>43.91455655866408</v>
+        <v>34.09315252537899</v>
       </c>
       <c r="D6" t="n">
-        <v>37.71580155404972</v>
+        <v>38.15856976866503</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
         <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.54355373745002</v>
       </c>
       <c r="D8" t="n">
-        <v>39.80496066868692</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.53906160508951</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>33.83593462686631</v>
+        <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
-        <v>41.82343394861835</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>32.88363935374691</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>49.93266998569701</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
         <v>47.08167465256428</v>
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.780555844801</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>45.78871292607123</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
         <v>43.71722527011046</v>
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.01314148535999</v>
+        <v>18.06019847711535</v>
       </c>
       <c r="C21" t="n">
-        <v>115.7987666915999</v>
+        <v>117.8212948268954</v>
       </c>
       <c r="D21" t="n">
-        <v>6.004380495119997</v>
+        <v>6.880075610329657</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.720063035569417</v>
+        <v>6.046584110456105</v>
       </c>
       <c r="C2" t="n">
-        <v>10.37216449536755</v>
+        <v>8.623671834103982</v>
       </c>
       <c r="D2" t="n">
-        <v>29.92759701625977</v>
+        <v>31.05955211925634</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.22614612934204</v>
+        <v>17.68127615348505</v>
       </c>
       <c r="C3" t="n">
-        <v>27.17477645355171</v>
+        <v>18.82501222893259</v>
       </c>
       <c r="D3" t="n">
-        <v>55.99398031171683</v>
+        <v>49.8335134675681</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.1628155546515</v>
+        <v>27.75891633757857</v>
       </c>
       <c r="C4" t="n">
-        <v>65.83011056056563</v>
+        <v>42.98484148274235</v>
       </c>
       <c r="D4" t="n">
-        <v>54.50957778289565</v>
+        <v>36.43756604312036</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.20699420134261</v>
+        <v>27.66074156715389</v>
       </c>
       <c r="C5" t="n">
-        <v>87.25282721493528</v>
+        <v>54.95332774521523</v>
       </c>
       <c r="D5" t="n">
-        <v>36.44738352016284</v>
+        <v>28.10252803406495</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.22770871412303</v>
+        <v>16.26166897314417</v>
       </c>
       <c r="C6" t="n">
-        <v>64.08063615159783</v>
+        <v>40.25165587411923</v>
       </c>
       <c r="D6" t="n">
-        <v>31.07427833482005</v>
+        <v>30.71201343195298</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.527640485537042</v>
+        <v>6.467753875577986</v>
       </c>
       <c r="C7" t="n">
-        <v>26.70942804173872</v>
+        <v>22.63713856452295</v>
       </c>
       <c r="D7" t="n">
-        <v>31.08115056874977</v>
+        <v>30.72183090899544</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.44213062427633</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>29.6242369756475</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.85468564423824</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>30.06405994715006</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>20.92595231602077</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
         <v>33.73775985644164</v>
@@ -5888,7 +5888,7 @@
         <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>33.93999988351647</v>
+        <v>34.47308888692249</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
         <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>29.65859814529614</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.030744876179508</v>
+        <v>7.058068521938676</v>
       </c>
       <c r="C21" t="n">
-        <v>65.03439010466045</v>
+        <v>66.16939239317509</v>
       </c>
       <c r="D21" t="n">
-        <v>4.394215547612193</v>
+        <v>5.293551391454007</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.727917017203391</v>
+        <v>6.807438581247383</v>
       </c>
       <c r="C2" t="n">
-        <v>8.902488182110076</v>
+        <v>3.854341486872978</v>
       </c>
       <c r="D2" t="n">
-        <v>29.43279617331937</v>
+        <v>38.79376053331271</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.47082229187775</v>
+        <v>19.89511722656161</v>
       </c>
       <c r="C3" t="n">
-        <v>35.48036203147973</v>
+        <v>28.41668729942393</v>
       </c>
       <c r="D3" t="n">
-        <v>67.60314691443537</v>
+        <v>63.88232311533996</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.85124167950677</v>
+        <v>32.34073287329843</v>
       </c>
       <c r="C4" t="n">
-        <v>67.2850606582594</v>
+        <v>45.28213111067988</v>
       </c>
       <c r="D4" t="n">
-        <v>71.20321574590842</v>
+        <v>53.74381457358314</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.69911184307752</v>
+        <v>35.95650966803944</v>
       </c>
       <c r="C5" t="n">
-        <v>107.6977231558751</v>
+        <v>70.29313562407164</v>
       </c>
       <c r="D5" t="n">
-        <v>48.44924920458011</v>
+        <v>35.68652904937156</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.38370878810704</v>
+        <v>28.73968229412113</v>
       </c>
       <c r="C6" t="n">
-        <v>106.5461330987936</v>
+        <v>68.46806664187682</v>
       </c>
       <c r="D6" t="n">
-        <v>35.54221213684728</v>
+        <v>32.92585450502953</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.25301317025519</v>
+        <v>13.95358012045992</v>
       </c>
       <c r="C7" t="n">
-        <v>63.65946638647593</v>
+        <v>43.77711188006952</v>
       </c>
       <c r="D7" t="n">
-        <v>33.53650157707104</v>
+        <v>33.29695513723482</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.175193059712437</v>
+        <v>6.258641614573416</v>
       </c>
       <c r="C8" t="n">
-        <v>27.95526587842792</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>31.71045084717197</v>
+        <v>32.3780392860598</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>30.95155987178918</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -6179,10 +6179,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.34243432679967</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
         <v>34.16482010778901</v>
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.909319358310797</v>
+        <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
         <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6238,10 +6238,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
@@ -6322,10 +6322,10 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.241755221221127</v>
+        <v>7.280805849943744</v>
       </c>
       <c r="C21" t="n">
-        <v>74.22799101751654</v>
+        <v>75.53836069316635</v>
       </c>
       <c r="D21" t="n">
-        <v>5.431316415915846</v>
+        <v>6.370705118700775</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.356816384998097</v>
+        <v>5.393721887131976</v>
       </c>
       <c r="C2" t="n">
-        <v>5.746169312956581</v>
+        <v>6.896777622333842</v>
       </c>
       <c r="D2" t="n">
-        <v>27.77266080543802</v>
+        <v>33.52373885691583</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.25622045527519</v>
+        <v>21.98623983660732</v>
       </c>
       <c r="C3" t="n">
-        <v>34.92567457858028</v>
+        <v>20.27799883121787</v>
       </c>
       <c r="D3" t="n">
-        <v>74.93680226515903</v>
+        <v>80.09588645097602</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.26714285320892</v>
+        <v>36.1950743601714</v>
       </c>
       <c r="C4" t="n">
-        <v>79.29478032431062</v>
+        <v>60.53358169615408</v>
       </c>
       <c r="D4" t="n">
-        <v>88.10105723140452</v>
+        <v>73.67918345601888</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.05592822807562</v>
+        <v>42.82874359776711</v>
       </c>
       <c r="C5" t="n">
-        <v>116.6807146497334</v>
+        <v>77.9998551024091</v>
       </c>
       <c r="D5" t="n">
-        <v>61.77647428973056</v>
+        <v>46.58392856651115</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.29190752999335</v>
+        <v>39.92964262712628</v>
       </c>
       <c r="C6" t="n">
-        <v>139.3109809803267</v>
+        <v>91.73352373711774</v>
       </c>
       <c r="D6" t="n">
-        <v>42.62650357069227</v>
+        <v>37.11202671593793</v>
       </c>
     </row>
     <row r="7">
@@ -6451,10 +6451,10 @@
         <v>24.73316991308989</v>
       </c>
       <c r="C7" t="n">
-        <v>111.0297748640888</v>
+        <v>74.49894278906496</v>
       </c>
       <c r="D7" t="n">
-        <v>36.05173919535137</v>
+        <v>35.39298648580176</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.93176068678823</v>
+        <v>11.09865779651019</v>
       </c>
       <c r="C8" t="n">
-        <v>57.07881152490955</v>
+        <v>43.56014563743097</v>
       </c>
       <c r="D8" t="n">
-        <v>33.88011327355743</v>
+        <v>34.46425315758427</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>29.28749751309084</v>
+        <v>28.51093507903161</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>33.41280136633594</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6538,7 +6538,7 @@
         <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6577,7 +6577,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.437319305054652</v>
+        <v>7.490326460471576</v>
       </c>
       <c r="C21" t="n">
-        <v>82.74017726873301</v>
+        <v>84.26617268030523</v>
       </c>
       <c r="D21" t="n">
-        <v>6.50765439192282</v>
+        <v>7.490326460471576</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_81_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_81_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497616665423</v>
+        <v>10.84497626661138</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907136501655</v>
+        <v>37.78907171331497</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.116288197457628</v>
+        <v>4.502294971675872</v>
       </c>
       <c r="C2" t="n">
-        <v>7.191301933607885</v>
+        <v>6.478553100324701</v>
       </c>
       <c r="D2" t="n">
-        <v>26.40803149653495</v>
+        <v>13.86325933166921</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.00801821255</v>
+        <v>15.4968875115359</v>
       </c>
       <c r="C3" t="n">
-        <v>23.85156047467626</v>
+        <v>28.24979018970197</v>
       </c>
       <c r="D3" t="n">
-        <v>87.184104875638</v>
+        <v>46.24522560854601</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.1815508764902</v>
+        <v>31.77917318646925</v>
       </c>
       <c r="C4" t="n">
-        <v>54.63720498444773</v>
+        <v>69.46748580480005</v>
       </c>
       <c r="D4" t="n">
-        <v>93.98467122295565</v>
+        <v>63.18822748843746</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.03829782712819</v>
+        <v>41.03705403751668</v>
       </c>
       <c r="C5" t="n">
-        <v>95.91675070491338</v>
+        <v>110.7165973464341</v>
       </c>
       <c r="D5" t="n">
-        <v>61.5801247488812</v>
+        <v>50.5109193834984</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.98626519880311</v>
+        <v>39.88939097125216</v>
       </c>
       <c r="C6" t="n">
-        <v>107.5524244956466</v>
+        <v>135.366318704663</v>
       </c>
       <c r="D6" t="n">
-        <v>42.62650357069227</v>
+        <v>41.25794727097221</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.17151241526948</v>
+        <v>28.56591295046944</v>
       </c>
       <c r="C7" t="n">
-        <v>104.801567428347</v>
+        <v>126.360747013607</v>
       </c>
       <c r="D7" t="n">
-        <v>38.32743037379547</v>
+        <v>37.96811071404115</v>
       </c>
     </row>
     <row r="8">
@@ -864,10 +864,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.02627050830318</v>
+        <v>14.77039421039326</v>
       </c>
       <c r="C8" t="n">
-        <v>71.8492057353028</v>
+        <v>86.78649705541802</v>
       </c>
       <c r="D8" t="n">
         <v>36.04977569994287</v>
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.653124265231384</v>
+        <v>7.543749359432489</v>
       </c>
       <c r="C9" t="n">
-        <v>41.3796839862988</v>
+        <v>46.26093357181394</v>
       </c>
       <c r="D9" t="n">
         <v>34.39062207976576</v>
@@ -892,10 +892,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.694136684631501</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
         <v>34.73423377625215</v>
@@ -909,7 +909,7 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.67528785626833</v>
       </c>
       <c r="D11" t="n">
         <v>36.60544490054656</v>
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>27.77167905773377</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -948,10 +948,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
         <v>31.03599017435442</v>
@@ -965,7 +965,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.685800131558699</v>
+        <v>7.695929116916166</v>
       </c>
       <c r="C21" t="n">
-        <v>93.19032659514922</v>
+        <v>94.27513168222302</v>
       </c>
       <c r="D21" t="n">
-        <v>8.646525148003535</v>
+        <v>8.657920256530687</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.95688521647115</v>
+        <v>7.031277057815656</v>
       </c>
       <c r="C2" t="n">
-        <v>11.98124898262807</v>
+        <v>6.735770998837365</v>
       </c>
       <c r="D2" t="n">
-        <v>24.72237068834318</v>
+        <v>14.64865749506666</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.16018910670825</v>
+        <v>15.21708941582556</v>
       </c>
       <c r="C3" t="n">
-        <v>25.82978209873358</v>
+        <v>26.50227927614264</v>
       </c>
       <c r="D3" t="n">
-        <v>87.42463306317848</v>
+        <v>46.2746780396734</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.63275390981624</v>
+        <v>30.38803668955152</v>
       </c>
       <c r="C4" t="n">
-        <v>56.5133248472634</v>
+        <v>69.96523189085319</v>
       </c>
       <c r="D4" t="n">
-        <v>112.7713952914226</v>
+        <v>69.96523189085319</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.30890034060182</v>
+        <v>44.08047192068179</v>
       </c>
       <c r="C5" t="n">
-        <v>98.2238578098934</v>
+        <v>118.1042488208913</v>
       </c>
       <c r="D5" t="n">
-        <v>77.41080647986101</v>
+        <v>60.54928965942204</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.03659637362695</v>
+        <v>47.69821221083129</v>
       </c>
       <c r="C6" t="n">
-        <v>127.8795107120768</v>
+        <v>155.290888362352</v>
       </c>
       <c r="D6" t="n">
-        <v>50.99884799250906</v>
+        <v>46.65166915810419</v>
       </c>
     </row>
     <row r="7">
@@ -1161,10 +1161,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>46.95110220789945</v>
+        <v>37.42913122440964</v>
       </c>
       <c r="C7" t="n">
-        <v>129.594623951396</v>
+        <v>158.8791762213741</v>
       </c>
       <c r="D7" t="n">
         <v>41.20198765183014</v>
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>28.12216298814988</v>
+        <v>22.28076414788136</v>
       </c>
       <c r="C8" t="n">
-        <v>103.0589652533089</v>
+        <v>126.0907663949391</v>
       </c>
       <c r="D8" t="n">
-        <v>38.21943812632832</v>
+        <v>37.80219535202343</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.42343636016663</v>
+        <v>11.09374905798895</v>
       </c>
       <c r="C9" t="n">
-        <v>64.12186955517615</v>
+        <v>74.88280614142545</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>35.94374694788421</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.975317438673588</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>39.57424995818893</v>
+        <v>42.70602513473626</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>35.3036474447153</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>37.13853390395258</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.37527396939631</v>
+        <v>30.8092064546734</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.09761929554372</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1259,10 +1259,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
         <v>31.34327720578367</v>
@@ -1276,7 +1276,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.86689983420503</v>
+        <v>7.879933146769599</v>
       </c>
       <c r="C21" t="n">
-        <v>101.2863353653898</v>
+        <v>103.424122551351</v>
       </c>
       <c r="D21" t="n">
-        <v>9.833624792756288</v>
+        <v>9.849916433461997</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10.10905611062941</v>
+        <v>9.069385291832035</v>
       </c>
       <c r="C2" t="n">
-        <v>13.22021458538755</v>
+        <v>8.832784095108552</v>
       </c>
       <c r="D2" t="n">
-        <v>28.99395494952105</v>
+        <v>16.25872373003143</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.78069471352124</v>
+        <v>18.87409961414493</v>
       </c>
       <c r="C3" t="n">
-        <v>35.43127464626738</v>
+        <v>26.14394136409256</v>
       </c>
       <c r="D3" t="n">
-        <v>86.3201668959008</v>
+        <v>46.68701207545707</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.70107533848601</v>
+        <v>29.18834099496192</v>
       </c>
       <c r="C4" t="n">
-        <v>60.03583561010095</v>
+        <v>68.02529842726149</v>
       </c>
       <c r="D4" t="n">
-        <v>126.9252519435489</v>
+        <v>75.56806603898974</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.92878405260905</v>
+        <v>44.96404485450392</v>
       </c>
       <c r="C5" t="n">
-        <v>99.64739198105129</v>
+        <v>121.6139968635737</v>
       </c>
       <c r="D5" t="n">
-        <v>94.39504176333082</v>
+        <v>68.77142668248908</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>63.31585468998956</v>
+        <v>52.68941753922207</v>
       </c>
       <c r="C6" t="n">
-        <v>139.1499743568302</v>
+        <v>170.0632460681538</v>
       </c>
       <c r="D6" t="n">
-        <v>61.26302024040947</v>
+        <v>53.61520562432682</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>56.47307319138927</v>
+        <v>45.75337000871835</v>
       </c>
       <c r="C7" t="n">
-        <v>154.507453694363</v>
+        <v>186.906109682212</v>
       </c>
       <c r="D7" t="n">
-        <v>45.09461729916874</v>
+        <v>44.19631814978291</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>37.55184968744049</v>
+        <v>30.12492830481337</v>
       </c>
       <c r="C8" t="n">
-        <v>132.3494080095125</v>
+        <v>163.0584761983527</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>40.05530633326986</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19.52499834206056</v>
+        <v>16.08593613408398</v>
       </c>
       <c r="C9" t="n">
-        <v>91.30155474724909</v>
+        <v>111.1593655610493</v>
       </c>
       <c r="D9" t="n">
-        <v>36.72030938194344</v>
+        <v>36.94218436310322</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>55.37547925804135</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.686282702997524</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>38.38240824523329</v>
+        <v>40.15937158992001</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>37.13853390395258</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
         <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
-        <v>36.45032876327558</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1562,7 +1562,7 @@
         <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1570,10 +1570,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
         <v>31.65056423721292</v>
@@ -1587,7 +1587,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -1601,7 +1601,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.032597705566523</v>
+        <v>8.048912783148422</v>
       </c>
       <c r="C21" t="n">
-        <v>109.4441437383439</v>
+        <v>111.6786648661843</v>
       </c>
       <c r="D21" t="n">
-        <v>11.04482184515397</v>
+        <v>11.06725507682908</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.196030745679874</v>
+        <v>8.068002633500289</v>
       </c>
       <c r="C2" t="n">
-        <v>8.988881980083795</v>
+        <v>5.934664872171968</v>
       </c>
       <c r="D2" t="n">
-        <v>23.85745096090174</v>
+        <v>13.36551324561608</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.82411259668635</v>
+        <v>21.622993186036</v>
       </c>
       <c r="C3" t="n">
-        <v>51.25213890020474</v>
+        <v>41.04687151455914</v>
       </c>
       <c r="D3" t="n">
-        <v>94.54721265748907</v>
+        <v>51.67429041303086</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.38054256081604</v>
+        <v>21.59452250261284</v>
       </c>
       <c r="C4" t="n">
-        <v>83.16188453133881</v>
+        <v>99.23014920674635</v>
       </c>
       <c r="D4" t="n">
-        <v>116.7788894201581</v>
+        <v>74.41942122502097</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.66198535676539</v>
+        <v>29.67332436085985</v>
       </c>
       <c r="C5" t="n">
-        <v>83.12948685709868</v>
+        <v>101.6108873895449</v>
       </c>
       <c r="D5" t="n">
-        <v>61.97282383057992</v>
+        <v>51.17359908386501</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.05919226635785</v>
+        <v>28.37741739125406</v>
       </c>
       <c r="C6" t="n">
-        <v>101.7561860497734</v>
+        <v>123.0895636630566</v>
       </c>
       <c r="D6" t="n">
-        <v>29.66547037922588</v>
+        <v>29.10194719698821</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.852943133008</v>
+        <v>19.94224111636546</v>
       </c>
       <c r="C7" t="n">
-        <v>93.06379187637214</v>
+        <v>114.6229714616321</v>
       </c>
       <c r="D7" t="n">
-        <v>28.38625312059227</v>
+        <v>28.14670668075605</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.51866588747858</v>
+        <v>11.09865779651019</v>
       </c>
       <c r="C8" t="n">
-        <v>67.25953521794897</v>
+        <v>81.86303231862027</v>
       </c>
       <c r="D8" t="n">
-        <v>27.03733177495716</v>
+        <v>27.20422888467911</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>42.26718391093791</v>
+        <v>47.37030847761284</v>
       </c>
       <c r="D9" t="n">
-        <v>27.73437264497238</v>
+        <v>27.62343515439249</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.128249096357838</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1845,7 @@
         <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>29.14219885286231</v>
+        <v>28.60910984945629</v>
       </c>
     </row>
     <row r="12">
@@ -1859,7 +1859,7 @@
         <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="13">
@@ -1867,10 +1867,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
         <v>26.01631416254048</v>
@@ -1884,7 +1884,7 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
         <v>23.66110142005238</v>
@@ -1898,7 +1898,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
         <v>22.57528845915541</v>
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>17.9443845382232</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>74.64718669240621</v>
       </c>
       <c r="D20" t="n">
         <v>7.397468951499714</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.428083056780614</v>
+        <v>4.785038310498954</v>
       </c>
       <c r="C2" t="n">
-        <v>3.835688280492288</v>
+        <v>3.141592653589793</v>
       </c>
       <c r="D2" t="n">
-        <v>16.46096375710627</v>
+        <v>9.776243638889738</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>30.92014394525329</v>
+        <v>25.20146356801562</v>
       </c>
       <c r="C3" t="n">
-        <v>44.28173020005238</v>
+        <v>32.67747233585509</v>
       </c>
       <c r="D3" t="n">
-        <v>92.46590752448583</v>
+        <v>50.7563563095601</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.55617758888499</v>
+        <v>30.37527396939631</v>
       </c>
       <c r="C4" t="n">
-        <v>106.9005440200267</v>
+        <v>103.5439486192068</v>
       </c>
       <c r="D4" t="n">
-        <v>135.2848336452105</v>
+        <v>82.77900292668257</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.46625771072178</v>
+        <v>32.7658296292373</v>
       </c>
       <c r="C5" t="n">
-        <v>117.0734137314322</v>
+        <v>142.0588928045135</v>
       </c>
       <c r="D5" t="n">
-        <v>81.55869053030378</v>
+        <v>62.0709986010046</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.09694064747573</v>
+        <v>33.73088762251191</v>
       </c>
       <c r="C6" t="n">
-        <v>118.9033914521482</v>
+        <v>144.825457835081</v>
       </c>
       <c r="D6" t="n">
-        <v>37.07177506006381</v>
+        <v>34.85793398698726</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.47555110394973</v>
+        <v>18.98405535702057</v>
       </c>
       <c r="C7" t="n">
-        <v>117.1980956898715</v>
+        <v>144.1470701714464</v>
       </c>
       <c r="D7" t="n">
-        <v>30.84160412891355</v>
+        <v>30.60205768907732</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.09865779651019</v>
+        <v>9.346238144429634</v>
       </c>
       <c r="C8" t="n">
-        <v>87.7044311588888</v>
+        <v>107.5651872158018</v>
       </c>
       <c r="D8" t="n">
-        <v>28.20561154301086</v>
+        <v>28.37250865273282</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>4.659374604355361</v>
       </c>
       <c r="C9" t="n">
-        <v>47.48124596819272</v>
+        <v>53.91562042182632</v>
       </c>
       <c r="D9" t="n">
-        <v>28.73281006019139</v>
+        <v>28.6218725696115</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>33.88011327355743</v>
       </c>
       <c r="D10" t="n">
         <v>30.17892442854695</v>
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>20.82875929330033</v>
+        <v>21.47965802121596</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2181,7 +2181,7 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
         <v>25.23582473766426</v>
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
         <v>15.29268398905256</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>64.99562501195582</v>
       </c>
       <c r="D19" t="n">
         <v>6.018113427032947</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.966080798707867</v>
+        <v>5.425137813667874</v>
       </c>
       <c r="C2" t="n">
-        <v>5.527239574909543</v>
+        <v>7.776423565338985</v>
       </c>
       <c r="D2" t="n">
-        <v>16.09575361112646</v>
+        <v>13.61291366708627</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.87748682561417</v>
+        <v>20.65597169735289</v>
       </c>
       <c r="C3" t="n">
-        <v>28.80447764260142</v>
+        <v>21.71625921793945</v>
       </c>
       <c r="D3" t="n">
-        <v>85.52495125546089</v>
+        <v>46.99135386377358</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.11545498513618</v>
+        <v>39.52614432068083</v>
       </c>
       <c r="C4" t="n">
-        <v>108.7000875619111</v>
+        <v>92.10855136014</v>
       </c>
       <c r="D4" t="n">
-        <v>148.3283336438336</v>
+        <v>88.75195595932014</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.95837535245669</v>
+        <v>38.97538385859838</v>
       </c>
       <c r="C5" t="n">
-        <v>156.2696908234861</v>
+        <v>166.4798669476529</v>
       </c>
       <c r="D5" t="n">
-        <v>106.4950822181728</v>
+        <v>76.0118160013093</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.93343074922303</v>
+        <v>39.24536447726626</v>
       </c>
       <c r="C6" t="n">
-        <v>151.8694976130519</v>
+        <v>185.3991269561932</v>
       </c>
       <c r="D6" t="n">
-        <v>50.47557646614552</v>
+        <v>44.63908636439822</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.01559445674349</v>
+        <v>27.5478405811655</v>
       </c>
       <c r="C7" t="n">
-        <v>144.0272969515283</v>
+        <v>176.9050458190497</v>
       </c>
       <c r="D7" t="n">
-        <v>33.83593462686632</v>
+        <v>33.35684174719388</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.43936530761284</v>
+        <v>13.76901155206151</v>
       </c>
       <c r="C8" t="n">
-        <v>118.8307421220339</v>
+        <v>146.9529051101838</v>
       </c>
       <c r="D8" t="n">
-        <v>29.79113408536946</v>
+        <v>30.29182541453534</v>
       </c>
     </row>
     <row r="9">
@@ -2433,10 +2433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.21093688769282</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>73.66249374504666</v>
+        <v>88.41717999217197</v>
       </c>
       <c r="D9" t="n">
         <v>29.39843500367073</v>
@@ -2447,10 +2447,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>42.99073196896783</v>
+        <v>46.97662764820988</v>
       </c>
       <c r="D10" t="n">
         <v>30.7483380970101</v>
@@ -2464,7 +2464,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>34.11769621798515</v>
       </c>
       <c r="D11" t="n">
         <v>30.20837685967435</v>
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>26.03594911662541</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.07347651356504</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.66637001147211</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.9050578767911</v>
+        <v>35.50686921949439</v>
       </c>
       <c r="D19" t="n">
         <v>4.212679398923063</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.548036203147973</v>
+        <v>3.150428382928014</v>
       </c>
       <c r="C2" t="n">
-        <v>2.580032966760618</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="D2" t="n">
-        <v>11.27831762638736</v>
+        <v>9.383544557191014</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.14746744428205</v>
+        <v>21.46591355335651</v>
       </c>
       <c r="C3" t="n">
-        <v>27.5331143656018</v>
+        <v>26.92443078896877</v>
       </c>
       <c r="D3" t="n">
-        <v>83.08039947188632</v>
+        <v>48.22344723260333</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>53.30988208830605</v>
+        <v>44.09519813624549</v>
       </c>
       <c r="C4" t="n">
-        <v>105.8284755269892</v>
+        <v>87.05451417867742</v>
       </c>
       <c r="D4" t="n">
-        <v>157.8620855997744</v>
+        <v>93.51245057721293</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.24093876483053</v>
+        <v>41.33157834879072</v>
       </c>
       <c r="C5" t="n">
-        <v>191.1953654020664</v>
+        <v>192.152569413707</v>
       </c>
       <c r="D5" t="n">
-        <v>112.72918014014</v>
+        <v>82.17228284545804</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.17115256237099</v>
+        <v>33.40887437551896</v>
       </c>
       <c r="C6" t="n">
-        <v>184.0305706564731</v>
+        <v>228.870915300242</v>
       </c>
       <c r="D6" t="n">
-        <v>49.59004003691489</v>
+        <v>44.63908636439822</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.89936301254809</v>
+        <v>9.102764713776425</v>
       </c>
       <c r="C7" t="n">
-        <v>153.6091545449772</v>
+        <v>189.9004401801648</v>
       </c>
       <c r="D7" t="n">
-        <v>34.07548106670254</v>
+        <v>33.95570784678443</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.006913291658733</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>90.37478491444013</v>
+        <v>111.2369236296849</v>
       </c>
       <c r="D8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.79389940203295</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>32.72655972106742</v>
+        <v>35.83280945730432</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>26.33538216642069</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
         <v>23.63066724122073</v>
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.7904711328347</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.27821981539612</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.82875929330033</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>9.506263020221864</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>28.80545939030567</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.96293993361265</v>
+        <v>30.49799243242716</v>
       </c>
       <c r="D18" t="n">
         <v>3.21031499288707</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.067380738694535</v>
+        <v>3.876921684070654</v>
       </c>
       <c r="C2" t="n">
-        <v>5.341689258806895</v>
+        <v>12.30817096814226</v>
       </c>
       <c r="D2" t="n">
-        <v>12.89918308609884</v>
+        <v>11.36372967665683</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.8839170911874</v>
+        <v>16.26265072084841</v>
       </c>
       <c r="C3" t="n">
-        <v>18.6384801651257</v>
+        <v>20.11601046001715</v>
       </c>
       <c r="D3" t="n">
-        <v>74.66191290796993</v>
+        <v>44.8020564833032</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.78286349757476</v>
+        <v>42.67853619901734</v>
       </c>
       <c r="C4" t="n">
-        <v>87.51397210426492</v>
+        <v>77.72496574521998</v>
       </c>
       <c r="D4" t="n">
-        <v>161.9844442099067</v>
+        <v>95.8607910857713</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>63.00365892003907</v>
+        <v>52.30260894374884</v>
       </c>
       <c r="C5" t="n">
-        <v>194.606938674324</v>
+        <v>178.5799074024948</v>
       </c>
       <c r="D5" t="n">
-        <v>136.7819988941869</v>
+        <v>94.6650223819987</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.44161620712438</v>
+        <v>42.86801350593698</v>
       </c>
       <c r="C6" t="n">
-        <v>238.8533259570235</v>
+        <v>266.2244519514246</v>
       </c>
       <c r="D6" t="n">
-        <v>67.09951034215676</v>
+        <v>57.43911293236815</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.81679839440012</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="C7" t="n">
-        <v>204.8122060599696</v>
+        <v>255.5361646952895</v>
       </c>
       <c r="D7" t="n">
-        <v>39.1059563032632</v>
+        <v>37.72856427420492</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.842781498600267</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>136.9390785268664</v>
+        <v>170.4853975809798</v>
       </c>
       <c r="D8" t="n">
-        <v>33.12907627980861</v>
+        <v>33.54631905411351</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>61.90311974357836</v>
+        <v>74.10624370736622</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>33.28124717396686</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>24.34439782220815</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.86995163914969</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.13520344574558</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.1456838753228</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>34.47210713921825</v>
       </c>
       <c r="D17" t="n">
         <v>4.722206457427158</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.027709919897163</v>
+        <v>2.641883072128167</v>
       </c>
       <c r="C2" t="n">
-        <v>3.351686662298611</v>
+        <v>5.767767762450011</v>
       </c>
       <c r="D2" t="n">
-        <v>9.612291772280519</v>
+        <v>8.485245407805182</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.95478285234242</v>
+        <v>15.13854959948582</v>
       </c>
       <c r="C3" t="n">
-        <v>19.98838325846506</v>
+        <v>33.65431130158066</v>
       </c>
       <c r="D3" t="n">
-        <v>69.38011025912209</v>
+        <v>43.80558256349268</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.29038600294135</v>
+        <v>39.15602543617979</v>
       </c>
       <c r="C4" t="n">
-        <v>72.46672504127406</v>
+        <v>67.09361985593127</v>
       </c>
       <c r="D4" t="n">
-        <v>164.4859373603276</v>
+        <v>96.62655429508382</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>68.94323253073227</v>
+        <v>57.62859023928778</v>
       </c>
       <c r="C5" t="n">
-        <v>186.8020444255619</v>
+        <v>170.824100538945</v>
       </c>
       <c r="D5" t="n">
-        <v>152.367243699105</v>
+        <v>103.9179944945249</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>61.06176196103888</v>
+        <v>51.11960296013142</v>
       </c>
       <c r="C6" t="n">
-        <v>273.5905049763884</v>
+        <v>285.8270083621207</v>
       </c>
       <c r="D6" t="n">
-        <v>81.8316163920844</v>
+        <v>66.29447722467438</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.60099382591507</v>
+        <v>18.26541603751191</v>
       </c>
       <c r="C7" t="n">
-        <v>255.6559379152077</v>
+        <v>308.7753609488898</v>
       </c>
       <c r="D7" t="n">
-        <v>43.47767883027424</v>
+        <v>41.68108053150257</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>174.4909282143068</v>
+        <v>218.5517651809037</v>
       </c>
       <c r="D8" t="n">
-        <v>34.13045893814036</v>
+        <v>35.38218726105504</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>71.77655640518853</v>
+        <v>88.30624250159208</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>32.31422568528377</v>
+        <v>33.88011327355743</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>25.62361508084176</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>24.34439782220815</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
         <v>19.96089432274615</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
         <v>16.3902779224005</v>
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>3.719842051391165</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.67548347825081</v>
+        <v>3.609886308515522</v>
       </c>
       <c r="C2" t="n">
-        <v>9.021279654323941</v>
+        <v>5.915029918087032</v>
       </c>
       <c r="D2" t="n">
-        <v>11.22333975494954</v>
+        <v>9.082148011987242</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.72483290537041</v>
+        <v>12.13931036301181</v>
       </c>
       <c r="C3" t="n">
-        <v>16.77806826557799</v>
+        <v>28.37741739125405</v>
       </c>
       <c r="D3" t="n">
-        <v>62.38024912784233</v>
+        <v>40.83579575814608</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.93455136564751</v>
+        <v>34.42105625859742</v>
       </c>
       <c r="C4" t="n">
-        <v>62.29483707757286</v>
+        <v>74.50876026610743</v>
       </c>
       <c r="D4" t="n">
-        <v>161.7674779672682</v>
+        <v>96.16709636949631</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>68.96777622333845</v>
+        <v>58.0212893209865</v>
       </c>
       <c r="C5" t="n">
-        <v>163.7800607609742</v>
+        <v>150.0110492089127</v>
       </c>
       <c r="D5" t="n">
-        <v>169.7687217568797</v>
+        <v>110.7656847316464</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>72.97625209977816</v>
+        <v>61.46427851978007</v>
       </c>
       <c r="C6" t="n">
-        <v>283.8546772242889</v>
+        <v>281.1175646248487</v>
       </c>
       <c r="D6" t="n">
-        <v>101.7561860497734</v>
+        <v>79.41651703963724</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.72856427420492</v>
+        <v>32.81786225756237</v>
       </c>
       <c r="C7" t="n">
-        <v>311.8894646667607</v>
+        <v>353.1513389285499</v>
       </c>
       <c r="D7" t="n">
-        <v>51.80191761458295</v>
+        <v>48.50815406683489</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.59796646734432</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
-        <v>240.2483894447582</v>
+        <v>297.3272009696677</v>
       </c>
       <c r="D8" t="n">
-        <v>37.21805546799658</v>
+        <v>37.63529824230147</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.884374755077128</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>124.2499894494763</v>
+        <v>156.4218617176442</v>
       </c>
       <c r="D9" t="n">
-        <v>33.50312215512664</v>
+        <v>34.16874709860598</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>50.1084028247572</v>
+        <v>58.2225476003571</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>27.18950266911542</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.8983245115816</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>24.87748682561417</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>11.98419422574081</v>
+      </c>
+      <c r="D14" t="n">
         <v>11.67690719431156</v>
-      </c>
-      <c r="D14" t="n">
-        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.118071766416875</v>
+        <v>5.228788272818512</v>
       </c>
       <c r="C2" t="n">
-        <v>7.674321804097318</v>
+        <v>7.880488821989147</v>
       </c>
       <c r="D2" t="n">
-        <v>6.949791998363171</v>
+        <v>6.289075793405067</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.058545009356314</v>
+        <v>2.554507526450201</v>
       </c>
       <c r="C2" t="n">
-        <v>5.196390598578367</v>
+        <v>3.360522391636832</v>
       </c>
       <c r="D2" t="n">
-        <v>8.260425183532663</v>
+        <v>6.683738370512286</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.15880644837651</v>
+        <v>16.24792450528471</v>
       </c>
       <c r="C3" t="n">
-        <v>24.59768872990384</v>
+        <v>31.10667600906019</v>
       </c>
       <c r="D3" t="n">
-        <v>67.65714303816894</v>
+        <v>44.59098072689013</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>53.23330576737479</v>
+        <v>45.51186007347363</v>
       </c>
       <c r="C4" t="n">
-        <v>90.95990654617123</v>
+        <v>103.2759314959475</v>
       </c>
       <c r="D4" t="n">
-        <v>165.609056733986</v>
+        <v>99.12804744550469</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.02509313861647</v>
+        <v>36.22649028670731</v>
       </c>
       <c r="C5" t="n">
-        <v>241.019061392592</v>
+        <v>230.6125357275758</v>
       </c>
       <c r="D5" t="n">
-        <v>152.6126806251667</v>
+        <v>104.5315868096792</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.42646371873739</v>
+        <v>20.36733787230433</v>
       </c>
       <c r="C6" t="n">
-        <v>261.0722399995374</v>
+        <v>290.4559487876444</v>
       </c>
       <c r="D6" t="n">
-        <v>79.5372720072596</v>
+        <v>66.69699378341556</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.006733365209485</v>
+        <v>6.28809404570082</v>
       </c>
       <c r="C7" t="n">
-        <v>168.9401266944954</v>
+        <v>209.0641553670625</v>
       </c>
       <c r="D7" t="n">
-        <v>32.75797564760332</v>
+        <v>32.63820242768521</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.002765316663493</v>
+        <v>1.752419652080557</v>
       </c>
       <c r="C8" t="n">
-        <v>91.54306468249383</v>
+        <v>115.2424542630118</v>
       </c>
       <c r="D8" t="n">
-        <v>24.61732368398877</v>
+        <v>25.11801501315464</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>38.162496759482</v>
+        <v>44.37499623195582</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>20.74531073843935</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.78007281871549</v>
+        <v>23.06125357275758</v>
       </c>
       <c r="D10" t="n">
-        <v>19.50241814486289</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.81497376771187</v>
+        <v>16.8811517745239</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>11.0652783745658</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>9.886199381765381</v>
+      </c>
+      <c r="D13" t="n">
         <v>9.626036240139976</v>
-      </c>
-      <c r="D13" t="n">
-        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
         <v>2.5083653843506</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.558475574996192</v>
+        <v>6.664103416427349</v>
       </c>
       <c r="C2" t="n">
-        <v>3.80132711084365</v>
+        <v>8.730682333866884</v>
       </c>
       <c r="D2" t="n">
-        <v>12.63509295365645</v>
+        <v>12.20901445001333</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.23458094805276</v>
+        <v>11.10847527355266</v>
       </c>
       <c r="C3" t="n">
-        <v>19.33552103514093</v>
+        <v>19.85584731839174</v>
       </c>
       <c r="D3" t="n">
-        <v>8.973174016815847</v>
+        <v>8.418486563916399</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4557,7 +4557,7 @@
         <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39809768923389</v>
+        <v>13.3986722359711</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14298202010684</v>
+        <v>70.14598994126045</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576246786968693</v>
+        <v>1.576314380702482</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.62345084992573</v>
+        <v>4.147884050442774</v>
       </c>
       <c r="C2" t="n">
-        <v>7.760715602071037</v>
+        <v>4.880267837810894</v>
       </c>
       <c r="D2" t="n">
-        <v>13.59818745152257</v>
+        <v>11.23904771821748</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.60964962880404</v>
+        <v>18.23105486786327</v>
       </c>
       <c r="C3" t="n">
-        <v>16.51299638543135</v>
+        <v>28.73575530330414</v>
       </c>
       <c r="D3" t="n">
-        <v>17.41620427333842</v>
+        <v>16.6357148484622</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.89708072197011</v>
+        <v>12.96692367769187</v>
       </c>
       <c r="C4" t="n">
-        <v>30.00515508489526</v>
+        <v>30.78368101436299</v>
       </c>
       <c r="D4" t="n">
-        <v>19.76945352041802</v>
+        <v>19.47591095684822</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.043417883165113</v>
+        <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.424156065963628</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
         <v>29.10881943091793</v>
@@ -4882,7 +4882,7 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
         <v>34.77743067523902</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44108895379843</v>
+        <v>15.44222586320111</v>
       </c>
       <c r="C21" t="n">
-        <v>86.14502258434915</v>
+        <v>86.15136534206933</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250755569220722</v>
+        <v>3.250994918568654</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.774639996379739</v>
+        <v>5.455571992499525</v>
       </c>
       <c r="C2" t="n">
-        <v>4.559236338522187</v>
+        <v>7.395505456091222</v>
       </c>
       <c r="D2" t="n">
-        <v>24.55056484009999</v>
+        <v>16.12029730373262</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.84250376115979</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="C3" t="n">
-        <v>24.81367322483813</v>
+        <v>22.82563412373834</v>
       </c>
       <c r="D3" t="n">
-        <v>24.25407703341745</v>
+        <v>21.76534660315179</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.3489877655599</v>
+        <v>25.52544031041707</v>
       </c>
       <c r="C4" t="n">
-        <v>36.69282044622454</v>
+        <v>55.020086589104</v>
       </c>
       <c r="D4" t="n">
-        <v>24.05772749256809</v>
+        <v>23.44511692511808</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>17.15604113171301</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="C5" t="n">
-        <v>33.89483948912113</v>
+        <v>34.70478134512475</v>
       </c>
       <c r="D5" t="n">
-        <v>29.550605897829</v>
+        <v>29.45243112740432</v>
       </c>
     </row>
     <row r="6">
@@ -5190,7 +5190,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
         <v>12.11574841810989</v>
@@ -5204,7 +5204,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
@@ -5218,7 +5218,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
         <v>29.87458264023044</v>
@@ -5232,7 +5232,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
@@ -5280,7 +5280,7 @@
         <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5294,7 +5294,7 @@
         <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>45.52854978444583</v>
       </c>
     </row>
     <row r="14">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73496335148302</v>
+        <v>16.73738225209661</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0832764440464</v>
+        <v>102.0980317377893</v>
       </c>
       <c r="D21" t="n">
-        <v>5.020489005444907</v>
+        <v>5.021214675628983</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.713771638716436</v>
+        <v>4.673119072214817</v>
       </c>
       <c r="C2" t="n">
-        <v>5.034402227377644</v>
+        <v>7.199155915241861</v>
       </c>
       <c r="D2" t="n">
-        <v>31.32364225169873</v>
+        <v>16.929257412032</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.26327261565417</v>
+        <v>17.50456156672063</v>
       </c>
       <c r="C3" t="n">
-        <v>20.69033286700153</v>
+        <v>26.20284622634737</v>
       </c>
       <c r="D3" t="n">
-        <v>37.51748851779185</v>
+        <v>29.17263303169397</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.31819373382976</v>
+        <v>28.66506946859837</v>
       </c>
       <c r="C4" t="n">
-        <v>50.88496525881643</v>
+        <v>55.67098531701964</v>
       </c>
       <c r="D4" t="n">
-        <v>30.43908757017236</v>
+        <v>28.76717122984004</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.45305302221007</v>
+        <v>24.86276061005048</v>
       </c>
       <c r="C5" t="n">
-        <v>51.86082247683777</v>
+        <v>71.52032025438015</v>
       </c>
       <c r="D5" t="n">
-        <v>31.24412068765475</v>
+        <v>30.97414006898687</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.61135108230528</v>
+        <v>10.94845039776043</v>
       </c>
       <c r="C6" t="n">
-        <v>34.09315252537899</v>
+        <v>34.73717901936489</v>
       </c>
       <c r="D6" t="n">
-        <v>38.15856976866503</v>
+        <v>38.11831811279092</v>
       </c>
     </row>
     <row r="7">
@@ -5515,7 +5515,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
         <v>21.19985992550562</v>
@@ -5557,7 +5557,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
         <v>33.31069960509428</v>
@@ -5571,7 +5571,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>9.062513057902304</v>
       </c>
       <c r="C11" t="n">
         <v>33.22921454564179</v>
@@ -5591,7 +5591,7 @@
         <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>46.86470840992573</v>
       </c>
     </row>
     <row r="13">
@@ -5605,7 +5605,7 @@
         <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>46.30903920932205</v>
       </c>
     </row>
     <row r="14">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06019847711535</v>
+        <v>18.0646594655312</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8212948268954</v>
+        <v>117.8503974656083</v>
       </c>
       <c r="D21" t="n">
-        <v>6.880075610329657</v>
+        <v>6.881775034488075</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.046584110456105</v>
+        <v>5.354451978962104</v>
       </c>
       <c r="C2" t="n">
-        <v>8.623671834103982</v>
+        <v>7.877543578876407</v>
       </c>
       <c r="D2" t="n">
-        <v>31.05955211925634</v>
+        <v>18.72192871998667</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.68127615348505</v>
+        <v>14.82439033412684</v>
       </c>
       <c r="C3" t="n">
-        <v>18.82501222893259</v>
+        <v>25.56471021858694</v>
       </c>
       <c r="D3" t="n">
-        <v>49.8335134675681</v>
+        <v>33.4432355451676</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.75891633757857</v>
+        <v>22.85803179797848</v>
       </c>
       <c r="C4" t="n">
-        <v>42.98484148274235</v>
+        <v>50.80838893788518</v>
       </c>
       <c r="D4" t="n">
-        <v>36.43756604312036</v>
+        <v>31.80469862677967</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.66074156715389</v>
+        <v>20.83759502263855</v>
       </c>
       <c r="C5" t="n">
-        <v>54.95332774521523</v>
+        <v>65.9489020327795</v>
       </c>
       <c r="D5" t="n">
-        <v>28.10252803406495</v>
+        <v>27.4889357189107</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.26166897314417</v>
+        <v>12.3572583533546</v>
       </c>
       <c r="C6" t="n">
-        <v>40.25165587411923</v>
+        <v>51.40136455125026</v>
       </c>
       <c r="D6" t="n">
-        <v>30.71201343195298</v>
+        <v>30.63151012020474</v>
       </c>
     </row>
     <row r="7">
@@ -5826,10 +5826,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.467753875577986</v>
+        <v>5.449681506274044</v>
       </c>
       <c r="C7" t="n">
-        <v>22.63713856452295</v>
+        <v>22.93657161431823</v>
       </c>
       <c r="D7" t="n">
         <v>30.72183090899544</v>
@@ -5857,7 +5857,7 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>21.96562313481813</v>
       </c>
       <c r="D9" t="n">
         <v>29.95312245657017</v>
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.6377194015997</v>
       </c>
       <c r="D10" t="n">
         <v>33.73775985644164</v>
@@ -5930,7 +5930,7 @@
         <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.058068521938676</v>
+        <v>7.061021280041128</v>
       </c>
       <c r="C21" t="n">
-        <v>66.16939239317509</v>
+        <v>66.19707450038557</v>
       </c>
       <c r="D21" t="n">
-        <v>5.293551391454007</v>
+        <v>5.295765960030846</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.807438581247383</v>
+        <v>4.665265090580843</v>
       </c>
       <c r="C2" t="n">
-        <v>3.854341486872978</v>
+        <v>7.207991644580082</v>
       </c>
       <c r="D2" t="n">
-        <v>38.79376053331271</v>
+        <v>16.06335593688631</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.89511722656161</v>
+        <v>17.28366833326509</v>
       </c>
       <c r="C3" t="n">
-        <v>28.41668729942393</v>
+        <v>29.00082718345078</v>
       </c>
       <c r="D3" t="n">
-        <v>63.88232311533996</v>
+        <v>41.51320167407638</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.34073287329843</v>
+        <v>26.75066144531709</v>
       </c>
       <c r="C4" t="n">
-        <v>45.28213111067988</v>
+        <v>59.37217416203011</v>
       </c>
       <c r="D4" t="n">
-        <v>53.74381457358314</v>
+        <v>42.47433267653401</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.95650966803944</v>
+        <v>29.08427573831176</v>
       </c>
       <c r="C5" t="n">
-        <v>70.29313562407164</v>
+        <v>83.47309855358506</v>
       </c>
       <c r="D5" t="n">
-        <v>35.68652904937156</v>
+        <v>33.4285093296039</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.73968229412113</v>
+        <v>21.69564251615027</v>
       </c>
       <c r="C6" t="n">
-        <v>68.46806664187682</v>
+        <v>83.44168262704918</v>
       </c>
       <c r="D6" t="n">
-        <v>32.92585450502953</v>
+        <v>32.6440929139107</v>
       </c>
     </row>
     <row r="7">
@@ -6137,10 +6137,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.95358012045992</v>
+        <v>10.77958979262998</v>
       </c>
       <c r="C7" t="n">
-        <v>43.77711188006952</v>
+        <v>53.29908286355933</v>
       </c>
       <c r="D7" t="n">
         <v>33.29695513723482</v>
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.258641614573416</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>25.86905200690345</v>
       </c>
       <c r="D8" t="n">
         <v>32.3780392860598</v>
@@ -6179,10 +6179,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
         <v>34.16482010778901</v>
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
         <v>32.97886888105885</v>
@@ -6224,7 +6224,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
         <v>31.21957699504857</v>
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>19.66637001147211</v>
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.280805849943744</v>
+        <v>7.285352652791761</v>
       </c>
       <c r="C21" t="n">
-        <v>75.53836069316635</v>
+        <v>75.58553377271453</v>
       </c>
       <c r="D21" t="n">
-        <v>6.370705118700775</v>
+        <v>6.374683571192791</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.393721887131976</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C2" t="n">
-        <v>6.896777622333842</v>
+        <v>7.204064653763095</v>
       </c>
       <c r="D2" t="n">
-        <v>33.52373885691583</v>
+        <v>15.08848046656923</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.98623983660732</v>
+        <v>16.68971097219578</v>
       </c>
       <c r="C3" t="n">
-        <v>20.27799883121787</v>
+        <v>28.71121161069797</v>
       </c>
       <c r="D3" t="n">
-        <v>80.09588645097602</v>
+        <v>44.72842540548468</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.1950743601714</v>
+        <v>30.98788453684632</v>
       </c>
       <c r="C4" t="n">
-        <v>60.53358169615408</v>
+        <v>66.63416193034375</v>
       </c>
       <c r="D4" t="n">
-        <v>73.67918345601888</v>
+        <v>53.33540752861647</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.82874359776711</v>
+        <v>35.53926689373454</v>
       </c>
       <c r="C5" t="n">
-        <v>77.9998551024091</v>
+        <v>98.81290643244149</v>
       </c>
       <c r="D5" t="n">
-        <v>46.58392856651115</v>
+        <v>41.67519004527711</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.92964262712628</v>
+        <v>31.27553661419064</v>
       </c>
       <c r="C6" t="n">
-        <v>91.73352373711774</v>
+        <v>111.1750735243173</v>
       </c>
       <c r="D6" t="n">
-        <v>37.11202671593793</v>
+        <v>36.22649028670731</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.73316991308989</v>
+        <v>19.04394196697963</v>
       </c>
       <c r="C7" t="n">
-        <v>74.49894278906496</v>
+        <v>90.72821408796898</v>
       </c>
       <c r="D7" t="n">
-        <v>35.39298648580176</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -6462,10 +6462,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.09865779651019</v>
+        <v>8.92899537012474</v>
       </c>
       <c r="C8" t="n">
-        <v>43.56014563743097</v>
+        <v>50.23603002630928</v>
       </c>
       <c r="D8" t="n">
         <v>34.46425315758427</v>
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>28.51093507903161</v>
+        <v>28.84374755077128</v>
       </c>
       <c r="D9" t="n">
         <v>32.72655972106742</v>
@@ -6490,10 +6490,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
         <v>34.30717352490479</v>
@@ -6524,7 +6524,7 @@
         <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
         <v>30.72870314292517</v>
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6594,7 +6594,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6633,7 +6633,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.490326460471576</v>
+        <v>7.497512193325517</v>
       </c>
       <c r="C21" t="n">
-        <v>84.26617268030523</v>
+        <v>85.28420119907776</v>
       </c>
       <c r="D21" t="n">
-        <v>7.490326460471576</v>
+        <v>7.497512193325517</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_81_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_81_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497626661138</v>
+        <v>10.84497632914288</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907171331497</v>
+        <v>37.78907193120454</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.502294971675872</v>
+        <v>0.7736171909464865</v>
       </c>
       <c r="C2" t="n">
-        <v>6.478553100324701</v>
+        <v>4.876340846993907</v>
       </c>
       <c r="D2" t="n">
-        <v>13.86325933166921</v>
+        <v>10.81689620539136</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.4968875115359</v>
+        <v>9.194067250271379</v>
       </c>
       <c r="C3" t="n">
-        <v>28.24979018970197</v>
+        <v>48.51306280535614</v>
       </c>
       <c r="D3" t="n">
-        <v>46.24522560854601</v>
+        <v>55.92034923389832</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.77917318646925</v>
+        <v>20.36930136771282</v>
       </c>
       <c r="C4" t="n">
-        <v>69.46748580480005</v>
+        <v>141.8193463646772</v>
       </c>
       <c r="D4" t="n">
-        <v>63.18822748843746</v>
+        <v>66.098127683825</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.03705403751668</v>
+        <v>20.10128424445345</v>
       </c>
       <c r="C5" t="n">
-        <v>110.7165973464341</v>
+        <v>196.0059291528758</v>
       </c>
       <c r="D5" t="n">
-        <v>50.5109193834984</v>
+        <v>42.092432819582</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.88939097125216</v>
+        <v>12.84027822384404</v>
       </c>
       <c r="C6" t="n">
-        <v>135.366318704663</v>
+        <v>144.825457835081</v>
       </c>
       <c r="D6" t="n">
-        <v>41.25794727097221</v>
+        <v>28.53842401475054</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.56591295046944</v>
+        <v>5.988660995905543</v>
       </c>
       <c r="C7" t="n">
-        <v>126.360747013607</v>
+        <v>70.00744704213579</v>
       </c>
       <c r="D7" t="n">
-        <v>37.96811071404115</v>
+        <v>28.62579956042849</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.77039421039326</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>86.78649705541802</v>
+        <v>31.71045084717197</v>
       </c>
       <c r="D8" t="n">
-        <v>36.04977569994287</v>
+        <v>30.62561963397925</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.543749359432489</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>46.26093357181394</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>34.27968458918587</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.274128593663113</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>29.04009709162065</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>37.86600895279948</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>30.38607319414302</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.96083756948391</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>22.56448923440869</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>37.31819373382975</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>35.38218726105505</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.9443845382232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>83.65177663575797</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.695929116916166</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>94.27513168222302</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.657920256530687</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.031277057815656</v>
+        <v>1.210494919336317</v>
       </c>
       <c r="C2" t="n">
-        <v>6.735770998837365</v>
+        <v>11.17032537892021</v>
       </c>
       <c r="D2" t="n">
-        <v>14.64865749506666</v>
+        <v>11.61211184583127</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.21708941582556</v>
+        <v>5.821763886183586</v>
       </c>
       <c r="C3" t="n">
-        <v>26.50227927614264</v>
+        <v>32.41730919422968</v>
       </c>
       <c r="D3" t="n">
-        <v>46.2746780396734</v>
+        <v>51.80682635310419</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.38803668955152</v>
+        <v>19.16960567312322</v>
       </c>
       <c r="C4" t="n">
-        <v>69.96523189085319</v>
+        <v>130.8816951916635</v>
       </c>
       <c r="D4" t="n">
-        <v>69.96523189085319</v>
+        <v>77.78877934599602</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.08047192068179</v>
+        <v>25.03456645829367</v>
       </c>
       <c r="C5" t="n">
-        <v>118.1042488208913</v>
+        <v>231.3733901983671</v>
       </c>
       <c r="D5" t="n">
-        <v>60.54928965942204</v>
+        <v>54.68334712654735</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.69821221083129</v>
+        <v>19.07928488433252</v>
       </c>
       <c r="C6" t="n">
-        <v>155.290888362352</v>
+        <v>226.174054356676</v>
       </c>
       <c r="D6" t="n">
-        <v>46.65166915810419</v>
+        <v>34.37491411649783</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.42913122440964</v>
+        <v>9.82140403328509</v>
       </c>
       <c r="C7" t="n">
-        <v>158.8791762213741</v>
+        <v>134.8047590178338</v>
       </c>
       <c r="D7" t="n">
-        <v>41.20198765183014</v>
+        <v>30.3625112492411</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22.28076414788136</v>
+        <v>6.342090169434394</v>
       </c>
       <c r="C8" t="n">
-        <v>126.0907663949391</v>
+        <v>59.08157684157305</v>
       </c>
       <c r="D8" t="n">
-        <v>37.80219535202343</v>
+        <v>31.87734795689393</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.09374905798895</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>74.88280614142545</v>
+        <v>34.72343455150543</v>
       </c>
       <c r="D9" t="n">
-        <v>35.94374694788421</v>
+        <v>34.61249706092553</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>42.70602513473626</v>
+        <v>32.74128593663113</v>
       </c>
       <c r="D10" t="n">
-        <v>35.3036474447153</v>
+        <v>38.43542262126263</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>37.84931924182727</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.8092064546734</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>21.5935407549086</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>27.9631198600619</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>24.38563122578652</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>43.93222801734051</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.879933146769599</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103.424122551351</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.849916433461997</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.069385291832035</v>
+        <v>0.6813329067472864</v>
       </c>
       <c r="C2" t="n">
-        <v>8.832784095108552</v>
+        <v>5.05992766768806</v>
       </c>
       <c r="D2" t="n">
-        <v>16.25872373003143</v>
+        <v>8.026769229921921</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.87409961414493</v>
+        <v>5.664684253504096</v>
       </c>
       <c r="C3" t="n">
-        <v>26.14394136409256</v>
+        <v>39.57424995818893</v>
       </c>
       <c r="D3" t="n">
-        <v>46.68701207545707</v>
+        <v>51.2619563772472</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.18834099496192</v>
+        <v>20.54797944988574</v>
       </c>
       <c r="C4" t="n">
-        <v>68.02529842726149</v>
+        <v>124.6151995954561</v>
       </c>
       <c r="D4" t="n">
-        <v>75.56806603898974</v>
+        <v>84.6168346290326</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.96404485450392</v>
+        <v>24.64186737659495</v>
       </c>
       <c r="C5" t="n">
-        <v>121.6139968635737</v>
+        <v>269.9560749752667</v>
       </c>
       <c r="D5" t="n">
-        <v>68.77142668248908</v>
+        <v>60.27930904075417</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.68941753922207</v>
+        <v>14.00757624419349</v>
       </c>
       <c r="C6" t="n">
-        <v>170.0632460681538</v>
+        <v>265.7816837368093</v>
       </c>
       <c r="D6" t="n">
-        <v>53.61520562432682</v>
+        <v>35.09944392223197</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>45.75337000871835</v>
+        <v>4.19206269713388</v>
       </c>
       <c r="C7" t="n">
-        <v>186.906109682212</v>
+        <v>119.3540136483975</v>
       </c>
       <c r="D7" t="n">
-        <v>44.19631814978291</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>30.12492830481337</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>163.0584761983527</v>
+        <v>44.06083696659685</v>
       </c>
       <c r="D8" t="n">
-        <v>40.05530633326986</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.08593613408398</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>111.1593655610493</v>
+        <v>24.96093538047515</v>
       </c>
       <c r="D9" t="n">
-        <v>36.94218436310322</v>
+        <v>39.49374664644068</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.114144775599888</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>62.06608986248335</v>
+        <v>25.90832191507333</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>29.60951076008381</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>40.15937158992001</v>
+        <v>21.50125647070939</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>33.62976760897449</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.43908757017236</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>23.15451960466103</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>20.89551813718911</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>37.98872741583033</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.048912783148422</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>111.6786648661843</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.06725507682908</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.068002633500289</v>
+        <v>1.27430852011236</v>
       </c>
       <c r="C2" t="n">
-        <v>5.934664872171968</v>
+        <v>5.613633372883262</v>
       </c>
       <c r="D2" t="n">
-        <v>13.36551324561608</v>
+        <v>10.26908098642164</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.622993186036</v>
+        <v>4.039891802975625</v>
       </c>
       <c r="C3" t="n">
-        <v>41.04687151455914</v>
+        <v>29.31498644880976</v>
       </c>
       <c r="D3" t="n">
-        <v>51.67429041303086</v>
+        <v>46.29922173227958</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.59452250261284</v>
+        <v>16.04273923509713</v>
       </c>
       <c r="C4" t="n">
-        <v>99.23014920674635</v>
+        <v>111.5844623169882</v>
       </c>
       <c r="D4" t="n">
-        <v>74.41942122502097</v>
+        <v>89.97717709422018</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.67332436085985</v>
+        <v>27.93072218582176</v>
       </c>
       <c r="C5" t="n">
-        <v>101.6108873895449</v>
+        <v>252.9472959991907</v>
       </c>
       <c r="D5" t="n">
-        <v>51.17359908386501</v>
+        <v>74.76008767839463</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.37741739125406</v>
+        <v>21.25287430153496</v>
       </c>
       <c r="C6" t="n">
-        <v>123.0895636630566</v>
+        <v>344.9164391853277</v>
       </c>
       <c r="D6" t="n">
-        <v>29.10194719698821</v>
+        <v>43.19002675292993</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.94224111636546</v>
+        <v>8.384125394267761</v>
       </c>
       <c r="C7" t="n">
-        <v>114.6229714616321</v>
+        <v>232.5397064710122</v>
       </c>
       <c r="D7" t="n">
-        <v>28.14670668075605</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.09865779651019</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>81.86303231862027</v>
+        <v>89.20650514638642</v>
       </c>
       <c r="D8" t="n">
-        <v>27.20422888467911</v>
+        <v>36.55046702910875</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>47.37030847761284</v>
+        <v>36.49843440078366</v>
       </c>
       <c r="D9" t="n">
-        <v>27.62343515439249</v>
+        <v>40.15937158992001</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>28.47068342315751</v>
       </c>
       <c r="D10" t="n">
-        <v>29.04009709162065</v>
+        <v>31.03304493124168</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>31.45225120095506</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
+        <v>20.03256190515617</v>
+      </c>
+      <c r="D13" t="n">
         <v>23.15451960466103</v>
-      </c>
-      <c r="D13" t="n">
-        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
         <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>20.58823110575986</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>38.02505208088746</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>45.33318199130072</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>74.64718669240621</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.785038310498954</v>
+        <v>0.7019496085364695</v>
       </c>
       <c r="C2" t="n">
-        <v>3.141592653589793</v>
+        <v>3.245657910239955</v>
       </c>
       <c r="D2" t="n">
-        <v>9.776243638889738</v>
+        <v>7.497607217332891</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.20146356801562</v>
+        <v>4.206788912697582</v>
       </c>
       <c r="C3" t="n">
-        <v>32.67747233585509</v>
+        <v>26.36974333606933</v>
       </c>
       <c r="D3" t="n">
-        <v>50.7563563095601</v>
+        <v>44.3848137089983</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.37527396939631</v>
+        <v>13.29875440172729</v>
       </c>
       <c r="C4" t="n">
-        <v>103.5439486192068</v>
+        <v>97.87730087029425</v>
       </c>
       <c r="D4" t="n">
-        <v>82.77900292668257</v>
+        <v>92.18512768107125</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.7658296292373</v>
+        <v>28.49522711576368</v>
       </c>
       <c r="C5" t="n">
-        <v>142.0588928045135</v>
+        <v>240.9699740073796</v>
       </c>
       <c r="D5" t="n">
-        <v>62.0709986010046</v>
+        <v>85.24024442122932</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.73088762251191</v>
+        <v>25.35854320069512</v>
       </c>
       <c r="C6" t="n">
-        <v>144.825457835081</v>
+        <v>384.9265851242022</v>
       </c>
       <c r="D6" t="n">
-        <v>34.85793398698726</v>
+        <v>50.35482149852316</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.98405535702057</v>
+        <v>8.144578954431539</v>
       </c>
       <c r="C7" t="n">
-        <v>144.1470701714464</v>
+        <v>317.0995997331985</v>
       </c>
       <c r="D7" t="n">
-        <v>30.60205768907732</v>
+        <v>38.20765715387736</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.346238144429634</v>
+        <v>4.005530633326986</v>
       </c>
       <c r="C8" t="n">
-        <v>107.5651872158018</v>
+        <v>134.8528646553419</v>
       </c>
       <c r="D8" t="n">
-        <v>28.37250865273282</v>
+        <v>37.80219535202343</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.659374604355361</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>53.91562042182632</v>
+        <v>44.92968368485526</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>40.04843409934012</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>33.88011327355743</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>32.02951885105219</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>25.41057582902019</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>32.34073287329842</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
         <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>16.28621266575034</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>38.85168364786328</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>64.99562501195582</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.425137813667874</v>
+        <v>0.7215845626214056</v>
       </c>
       <c r="C2" t="n">
-        <v>7.776423565338985</v>
+        <v>7.032258805519903</v>
       </c>
       <c r="D2" t="n">
-        <v>13.61291366708627</v>
+        <v>13.7729385428785</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.65597169735289</v>
+        <v>3.328124717396687</v>
       </c>
       <c r="C3" t="n">
-        <v>21.71625921793945</v>
+        <v>19.7625812864883</v>
       </c>
       <c r="D3" t="n">
-        <v>46.99135386377358</v>
+        <v>40.71307729511523</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.52614432068083</v>
+        <v>10.82278669161684</v>
       </c>
       <c r="C4" t="n">
-        <v>92.10855136014</v>
+        <v>83.17464725149402</v>
       </c>
       <c r="D4" t="n">
-        <v>88.75195595932014</v>
+        <v>92.72116192759002</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.97538385859838</v>
+        <v>25.30454707696154</v>
       </c>
       <c r="C5" t="n">
-        <v>166.4798669476529</v>
+        <v>214.1682616814417</v>
       </c>
       <c r="D5" t="n">
-        <v>76.0118160013093</v>
+        <v>94.19869222248147</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.24536447726626</v>
+        <v>30.43025184083414</v>
       </c>
       <c r="C6" t="n">
-        <v>185.3991269561932</v>
+        <v>385.6511149299363</v>
       </c>
       <c r="D6" t="n">
-        <v>44.63908636439822</v>
+        <v>61.70578845502478</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.5478405811655</v>
+        <v>15.75017841923158</v>
       </c>
       <c r="C7" t="n">
-        <v>176.9050458190497</v>
+        <v>417.7689910743707</v>
       </c>
       <c r="D7" t="n">
-        <v>33.35684174719388</v>
+        <v>42.4596064609703</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.76901155206151</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>146.9529051101838</v>
+        <v>244.4208171878071</v>
       </c>
       <c r="D8" t="n">
-        <v>30.29182541453534</v>
+        <v>39.22082078466007</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.212499472473814</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>88.41717999217197</v>
+        <v>88.74999246391164</v>
       </c>
       <c r="D9" t="n">
-        <v>29.39843500367073</v>
+        <v>41.04687151455913</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>46.97662764820988</v>
+        <v>38.57777603837842</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>33.31069960509428</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>34.11769621798515</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>32.87382187670443</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>26.03594911662541</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>29.07347651356504</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2601631416254048</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>19.51223562190536</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
+        <v>19.97365704290136</v>
+      </c>
+      <c r="D14" t="n">
         <v>16.59349969717959</v>
-      </c>
-      <c r="D14" t="n">
-        <v>19.66637001147211</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>34.04210164475815</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.150428382928014</v>
+        <v>0.5134540493210819</v>
       </c>
       <c r="C2" t="n">
-        <v>3.583379120500858</v>
+        <v>3.993749660876024</v>
       </c>
       <c r="D2" t="n">
-        <v>9.383544557191014</v>
+        <v>10.13654504634832</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.46591355335651</v>
+        <v>4.462043315801753</v>
       </c>
       <c r="C3" t="n">
-        <v>26.92443078896877</v>
+        <v>25.0394751968149</v>
       </c>
       <c r="D3" t="n">
-        <v>48.22344723260333</v>
+        <v>45.88688769649592</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.09519813624549</v>
+        <v>17.59979109403257</v>
       </c>
       <c r="C4" t="n">
-        <v>87.05451417867742</v>
+        <v>119.4845860930623</v>
       </c>
       <c r="D4" t="n">
-        <v>93.51245057721293</v>
+        <v>94.53346818962962</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.33157834879072</v>
+        <v>17.84326452468578</v>
       </c>
       <c r="C5" t="n">
-        <v>192.152569413707</v>
+        <v>324.1485482496907</v>
       </c>
       <c r="D5" t="n">
-        <v>82.17228284545804</v>
+        <v>86.24653581808231</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.40887437551896</v>
+        <v>9.781152377410974</v>
       </c>
       <c r="C6" t="n">
-        <v>228.870915300242</v>
+        <v>350.752929287075</v>
       </c>
       <c r="D6" t="n">
-        <v>44.63908636439822</v>
+        <v>54.54099370943156</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.102764713776425</v>
+        <v>3.593196597543325</v>
       </c>
       <c r="C7" t="n">
-        <v>189.9004401801648</v>
+        <v>171.8745705824891</v>
       </c>
       <c r="D7" t="n">
-        <v>33.95570784678443</v>
+        <v>32.93763547748049</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.255876297909922</v>
+        <v>2.002765316663493</v>
       </c>
       <c r="C8" t="n">
-        <v>111.2369236296849</v>
+        <v>65.42366701100744</v>
       </c>
       <c r="D8" t="n">
-        <v>31.79389940203295</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>0.9984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>35.83280945730432</v>
+        <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>25.4046853427947</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>25.76596849795754</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.7904711328347</v>
+        <v>19.01350778814797</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>15.4046032273367</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
+        <v>16.3902779224005</v>
+      </c>
+      <c r="D13" t="n">
         <v>13.52848336452105</v>
-      </c>
-      <c r="D13" t="n">
-        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.876921684070654</v>
+        <v>0.279798095710341</v>
       </c>
       <c r="C2" t="n">
-        <v>12.30817096814226</v>
+        <v>2.468113728476481</v>
       </c>
       <c r="D2" t="n">
-        <v>11.36372967665683</v>
+        <v>7.956083395216151</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.26265072084841</v>
+        <v>3.175953823238432</v>
       </c>
       <c r="C3" t="n">
-        <v>20.11601046001715</v>
+        <v>20.16018910670825</v>
       </c>
       <c r="D3" t="n">
-        <v>44.8020564833032</v>
+        <v>43.31470871136928</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.67853619901734</v>
+        <v>12.4181267110179</v>
       </c>
       <c r="C4" t="n">
-        <v>77.72496574521998</v>
+        <v>88.6881423585441</v>
       </c>
       <c r="D4" t="n">
-        <v>95.8607910857713</v>
+        <v>91.68738159501812</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.30260894374884</v>
+        <v>16.76334205001429</v>
       </c>
       <c r="C5" t="n">
-        <v>178.5799074024948</v>
+        <v>248.1858196335937</v>
       </c>
       <c r="D5" t="n">
-        <v>94.6650223819987</v>
+        <v>89.16723523821656</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.86801350593698</v>
+        <v>9.620145753914496</v>
       </c>
       <c r="C6" t="n">
-        <v>266.2244519514246</v>
+        <v>348.5793398698725</v>
       </c>
       <c r="D6" t="n">
-        <v>57.43911293236815</v>
+        <v>55.58753676215866</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.40326162673396</v>
+        <v>2.934443887993716</v>
       </c>
       <c r="C7" t="n">
-        <v>255.5361646952895</v>
+        <v>219.6640853298153</v>
       </c>
       <c r="D7" t="n">
-        <v>37.72856427420492</v>
+        <v>30.96137734883166</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.841398840268521</v>
+        <v>1.001382658331746</v>
       </c>
       <c r="C8" t="n">
-        <v>170.4853975809798</v>
+        <v>78.69198723390308</v>
       </c>
       <c r="D8" t="n">
-        <v>33.54631905411351</v>
+        <v>25.70215489718149</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>74.10624370736622</v>
+        <v>28.17812260729194</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>20.07968579496001</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>15.65887588273663</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>19.50241814486289</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>12.26104707833841</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>16.8811517745239</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>11.0652783745658</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>13.0179745583127</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>2.458296251434013</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.47210713921825</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.641883072128167</v>
+        <v>0.3229949946972006</v>
       </c>
       <c r="C2" t="n">
-        <v>5.767767762450011</v>
+        <v>6.686683613625026</v>
       </c>
       <c r="D2" t="n">
-        <v>8.485245407805182</v>
+        <v>12.14618259694154</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.13854959948582</v>
+        <v>1.988039101099791</v>
       </c>
       <c r="C3" t="n">
-        <v>33.65431130158066</v>
+        <v>14.3286077434822</v>
       </c>
       <c r="D3" t="n">
-        <v>43.80558256349268</v>
+        <v>40.14366362665208</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.15602543617979</v>
+        <v>9.291260272991813</v>
       </c>
       <c r="C4" t="n">
-        <v>67.09361985593127</v>
+        <v>68.0380611474167</v>
       </c>
       <c r="D4" t="n">
-        <v>96.62655429508382</v>
+        <v>91.63633071439729</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.62859023928778</v>
+        <v>17.9905266803228</v>
       </c>
       <c r="C5" t="n">
-        <v>170.824100538945</v>
+        <v>204.2526098685489</v>
       </c>
       <c r="D5" t="n">
-        <v>103.9179944945249</v>
+        <v>101.5127126191202</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.11960296013142</v>
+        <v>15.49688751153591</v>
       </c>
       <c r="C6" t="n">
-        <v>285.8270083621207</v>
+        <v>376.393234078889</v>
       </c>
       <c r="D6" t="n">
-        <v>66.29447722467438</v>
+        <v>69.59511300635215</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.26541603751191</v>
+        <v>6.707300315414209</v>
       </c>
       <c r="C7" t="n">
-        <v>308.7753609488898</v>
+        <v>357.2236284057657</v>
       </c>
       <c r="D7" t="n">
-        <v>41.68108053150257</v>
+        <v>38.74663664350886</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>1.835868206941535</v>
       </c>
       <c r="C8" t="n">
-        <v>218.5517651809037</v>
+        <v>179.6647386156875</v>
       </c>
       <c r="D8" t="n">
-        <v>35.38218726105504</v>
+        <v>27.95526587842792</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>88.30624250159208</v>
+        <v>59.79530742256046</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>21.96562313481813</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>33.88011327355743</v>
+        <v>23.63066724122073</v>
       </c>
       <c r="D10" t="n">
-        <v>25.62361508084176</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>14.9264920953685</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>17.59193711239859</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>12.36707583039707</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>15.67163860289184</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.609886308515522</v>
+        <v>0.3347759671481623</v>
       </c>
       <c r="C2" t="n">
-        <v>5.915029918087032</v>
+        <v>13.87700379952866</v>
       </c>
       <c r="D2" t="n">
-        <v>9.082148011987242</v>
+        <v>11.95277829920492</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.13931036301181</v>
+        <v>1.52661768010379</v>
       </c>
       <c r="C3" t="n">
-        <v>28.37741739125405</v>
+        <v>20.12091919853838</v>
       </c>
       <c r="D3" t="n">
-        <v>40.83579575814608</v>
+        <v>40.24183839707676</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.42105625859742</v>
+        <v>6.623851760553229</v>
       </c>
       <c r="C4" t="n">
-        <v>74.50876026610743</v>
+        <v>51.48481310611123</v>
       </c>
       <c r="D4" t="n">
-        <v>96.16709636949631</v>
+        <v>90.9216183857056</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.0212893209865</v>
+        <v>16.22338081267855</v>
       </c>
       <c r="C5" t="n">
-        <v>150.0110492089127</v>
+        <v>166.1607989437727</v>
       </c>
       <c r="D5" t="n">
-        <v>110.7656847316464</v>
+        <v>109.8821117978243</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>61.46427851978007</v>
+        <v>19.52205309894783</v>
       </c>
       <c r="C6" t="n">
-        <v>281.1175646248487</v>
+        <v>354.456081627494</v>
       </c>
       <c r="D6" t="n">
-        <v>79.41651703963724</v>
+        <v>81.91211970383264</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.81786225756237</v>
+        <v>11.73777555197486</v>
       </c>
       <c r="C7" t="n">
-        <v>353.1513389285499</v>
+        <v>444.4784191161094</v>
       </c>
       <c r="D7" t="n">
-        <v>48.50815406683489</v>
+        <v>47.84940135728529</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>297.3272009696677</v>
+        <v>310.5120726377024</v>
       </c>
       <c r="D8" t="n">
-        <v>37.63529824230147</v>
+        <v>30.95941385342316</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>0.9984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>156.4218617176442</v>
+        <v>129.3531140161512</v>
       </c>
       <c r="D9" t="n">
-        <v>34.16874709860598</v>
+        <v>23.74062298409636</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>58.2225476003571</v>
+        <v>43.84485247166256</v>
       </c>
       <c r="D10" t="n">
-        <v>27.18950266911542</v>
+        <v>20.64124548178919</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>20.07968579496001</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>18.12502611580461</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>14.31977201414398</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>3.380157345721768</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>7.166758241001715</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.228788272818512</v>
+        <v>7.05778424583032</v>
       </c>
       <c r="C2" t="n">
-        <v>7.880488821989147</v>
+        <v>27.49875319595316</v>
       </c>
       <c r="D2" t="n">
-        <v>6.289075793405067</v>
+        <v>8.527460559087794</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.554507526450201</v>
+        <v>0.3200497515844601</v>
       </c>
       <c r="C2" t="n">
-        <v>3.360522391636832</v>
+        <v>13.66985503393259</v>
       </c>
       <c r="D2" t="n">
-        <v>6.683738370512286</v>
+        <v>11.65825398793087</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.24792450528471</v>
+        <v>1.310633185169492</v>
       </c>
       <c r="C3" t="n">
-        <v>31.10667600906019</v>
+        <v>35.23983384393926</v>
       </c>
       <c r="D3" t="n">
-        <v>44.59098072689013</v>
+        <v>40.00621894805752</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.51186007347363</v>
+        <v>4.913647259755287</v>
       </c>
       <c r="C4" t="n">
-        <v>103.2759314959475</v>
+        <v>50.75733805726435</v>
       </c>
       <c r="D4" t="n">
-        <v>99.12804744550469</v>
+        <v>90.13032973608269</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.22649028670731</v>
+        <v>13.67083678163684</v>
       </c>
       <c r="C5" t="n">
-        <v>230.6125357275758</v>
+        <v>134.0331053222958</v>
       </c>
       <c r="D5" t="n">
-        <v>104.5315868096792</v>
+        <v>114.2018016965102</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.36733787230433</v>
+        <v>20.40758952817845</v>
       </c>
       <c r="C6" t="n">
-        <v>290.4559487876444</v>
+        <v>315.653485364843</v>
       </c>
       <c r="D6" t="n">
-        <v>66.69699378341556</v>
+        <v>94.02786812194252</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.28809404570082</v>
+        <v>16.28915790886308</v>
       </c>
       <c r="C7" t="n">
-        <v>209.0641553670625</v>
+        <v>476.7573018840403</v>
       </c>
       <c r="D7" t="n">
-        <v>32.63820242768521</v>
+        <v>56.2934133615121</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.752419652080557</v>
+        <v>7.260024272905162</v>
       </c>
       <c r="C8" t="n">
-        <v>115.2424542630118</v>
+        <v>422.3331361514141</v>
       </c>
       <c r="D8" t="n">
-        <v>25.11801501315464</v>
+        <v>35.13184159647211</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>44.37499623195582</v>
+        <v>231.970292802549</v>
       </c>
       <c r="D9" t="n">
-        <v>20.74531073843935</v>
+        <v>25.29374785221481</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>23.06125357275758</v>
+        <v>85.69675710370409</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>21.49536598448391</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.8811517745239</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>18.48041878474196</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.0652783745658</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>14.53673825678252</v>
       </c>
     </row>
     <row r="13">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
         <v>9.626036240139976</v>
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>3.994731408580272</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>10.0334615374024</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.479894700927443</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.664103416427349</v>
+        <v>5.65093978564464</v>
       </c>
       <c r="C2" t="n">
-        <v>8.730682333866884</v>
+        <v>15.71090851106171</v>
       </c>
       <c r="D2" t="n">
-        <v>12.20901445001333</v>
+        <v>14.90587539357932</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.10847527355266</v>
+        <v>11.36863841517807</v>
       </c>
       <c r="C3" t="n">
-        <v>19.85584731839174</v>
+        <v>53.21072557017713</v>
       </c>
       <c r="D3" t="n">
-        <v>8.418486563916399</v>
+        <v>8.860273030827463</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.657010198319369</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.29576810088555</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.675483478250811</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.63749841742144</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>35.05624702324509</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>45.69544689416779</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.3986722359711</v>
+        <v>11.67589810997788</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14598994126045</v>
+        <v>59.93627696455312</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576314380702482</v>
+        <v>0.7783932073318587</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.147884050442774</v>
+        <v>3.262347621212151</v>
       </c>
       <c r="C2" t="n">
-        <v>4.880267837810894</v>
+        <v>8.314421307266237</v>
       </c>
       <c r="D2" t="n">
-        <v>11.23904771821748</v>
+        <v>22.79225470179395</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.23105486786327</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="C3" t="n">
-        <v>28.73575530330414</v>
+        <v>58.60542920501334</v>
       </c>
       <c r="D3" t="n">
-        <v>16.6357148484622</v>
+        <v>19.74785507092459</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.96692367769187</v>
+        <v>13.71992416684918</v>
       </c>
       <c r="C4" t="n">
-        <v>30.78368101436299</v>
+        <v>85.61232680113885</v>
       </c>
       <c r="D4" t="n">
-        <v>19.47591095684822</v>
+        <v>18.850537669243</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.129631754689585</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.474225198880216</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.72581465307466</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.3497485290859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.06307819944583</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.44489594093983</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>6.989061906533041</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>21.07812321017901</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.94374694788421</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.18020927588745</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44222586320111</v>
+        <v>13.61947045585385</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15136534206933</v>
+        <v>73.70536952579729</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250994918568654</v>
+        <v>1.602290641865159</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.455571992499525</v>
+        <v>3.594178345247573</v>
       </c>
       <c r="C2" t="n">
-        <v>7.395505456091222</v>
+        <v>5.843362335677015</v>
       </c>
       <c r="D2" t="n">
-        <v>16.12029730373262</v>
+        <v>19.83523061660256</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.05157496443535</v>
+        <v>13.56284453416968</v>
       </c>
       <c r="C3" t="n">
-        <v>22.82563412373834</v>
+        <v>42.45567947015331</v>
       </c>
       <c r="D3" t="n">
-        <v>21.76534660315179</v>
+        <v>33.39905689847649</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.52544031041707</v>
+        <v>24.3767954964483</v>
       </c>
       <c r="C4" t="n">
-        <v>55.020086589104</v>
+        <v>122.279621807053</v>
       </c>
       <c r="D4" t="n">
-        <v>23.44511692511808</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.70734137314322</v>
+        <v>11.97732199181109</v>
       </c>
       <c r="C5" t="n">
-        <v>34.70478134512475</v>
+        <v>93.83053683338892</v>
       </c>
       <c r="D5" t="n">
-        <v>29.45243112740432</v>
+        <v>26.94897448157495</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.11574841810989</v>
+        <v>10.70694046251572</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>32.08056973167303</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.82246789644735</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>32.09922293805371</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>7.42692138262712</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.61594102565702</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>34.13045893814036</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>23.85156047467625</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.83124687252333</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>43.84485247166256</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.219371706403542</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.60177995163684</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>41.8744848292392</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.52854978444583</v>
+        <v>40.58545009356315</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73738225209661</v>
+        <v>14.81341037838875</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0980317377893</v>
+        <v>87.23452778384485</v>
       </c>
       <c r="D21" t="n">
-        <v>5.021214675628983</v>
+        <v>2.468901729731458</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.673119072214817</v>
+        <v>2.426880324898115</v>
       </c>
       <c r="C2" t="n">
-        <v>7.199155915241861</v>
+        <v>9.3413294059084</v>
       </c>
       <c r="D2" t="n">
-        <v>16.929257412032</v>
+        <v>24.18044595559894</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.50456156672063</v>
+        <v>12.88052987971815</v>
       </c>
       <c r="C3" t="n">
-        <v>26.20284622634737</v>
+        <v>31.01831871567798</v>
       </c>
       <c r="D3" t="n">
-        <v>29.17263303169397</v>
+        <v>41.04196277603791</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.66506946859837</v>
+        <v>25.53820303057228</v>
       </c>
       <c r="C4" t="n">
-        <v>55.67098531701964</v>
+        <v>113.3329549782518</v>
       </c>
       <c r="D4" t="n">
-        <v>28.76717122984004</v>
+        <v>34.98261594542659</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.86276061005048</v>
+        <v>24.15099352447154</v>
       </c>
       <c r="C5" t="n">
-        <v>71.52032025438015</v>
+        <v>164.2218472278852</v>
       </c>
       <c r="D5" t="n">
-        <v>30.97414006898687</v>
+        <v>29.28062527916113</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.94845039776043</v>
+        <v>10.38492721552276</v>
       </c>
       <c r="C6" t="n">
-        <v>34.73717901936489</v>
+        <v>83.40143097117505</v>
       </c>
       <c r="D6" t="n">
-        <v>38.11831811279092</v>
+        <v>33.73088762251191</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>17.84620976779852</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>34.01559445674349</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>25.45180923259856</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>35.46563581591602</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>27.29062268265283</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>37.71874679716245</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>43.41779222031519</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.062513057902304</v>
+        <v>6.574764375340887</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.4902616239802</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>42.95931604243193</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>46.30903920932205</v>
+        <v>40.84561323518855</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>26.11939767148639</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.44199175555609</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.0646594655312</v>
+        <v>16.02897956816018</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8503974656083</v>
+        <v>100.392029926898</v>
       </c>
       <c r="D21" t="n">
-        <v>6.881775034488075</v>
+        <v>3.374522014349512</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.354451978962104</v>
+        <v>1.762237129123025</v>
       </c>
       <c r="C2" t="n">
-        <v>7.877543578876407</v>
+        <v>6.413757751844412</v>
       </c>
       <c r="D2" t="n">
-        <v>18.72192871998667</v>
+        <v>18.96147515982289</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.82439033412684</v>
+        <v>10.52433538952581</v>
       </c>
       <c r="C3" t="n">
-        <v>25.56471021858694</v>
+        <v>33.72303364087794</v>
       </c>
       <c r="D3" t="n">
-        <v>33.4432355451676</v>
+        <v>49.71570374305848</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.85803179797848</v>
+        <v>24.88730430265664</v>
       </c>
       <c r="C4" t="n">
-        <v>50.80838893788518</v>
+        <v>94.64833267102649</v>
       </c>
       <c r="D4" t="n">
-        <v>31.80469862677967</v>
+        <v>46.30314872309656</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.83759502263855</v>
+        <v>30.9495963763807</v>
       </c>
       <c r="C5" t="n">
-        <v>65.9489020327795</v>
+        <v>185.0103548653114</v>
       </c>
       <c r="D5" t="n">
-        <v>27.4889357189107</v>
+        <v>34.28753857081986</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.3572583533546</v>
+        <v>20.48809283992669</v>
       </c>
       <c r="C6" t="n">
-        <v>51.40136455125026</v>
+        <v>169.9827427564055</v>
       </c>
       <c r="D6" t="n">
-        <v>30.63151012020474</v>
+        <v>35.58246379272141</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.449681506274044</v>
+        <v>9.162651323735481</v>
       </c>
       <c r="C7" t="n">
-        <v>22.93657161431823</v>
+        <v>66.71368349438775</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>36.17151241526948</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>24.86766934857171</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>36.46701847424777</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.098436812331936</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>30.06405994715006</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>38.71718421238145</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>43.13308538608361</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>6.930157044278233</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.03068052520567</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>46.20104696185489</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>5.858088551240717</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>30.8092064546734</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>26.87534340375643</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.061021280041128</v>
+        <v>17.25847647927468</v>
       </c>
       <c r="C21" t="n">
-        <v>66.19707450038557</v>
+        <v>113.0430209392492</v>
       </c>
       <c r="D21" t="n">
-        <v>5.295765960030846</v>
+        <v>4.314619119818671</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.665265090580843</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C2" t="n">
-        <v>7.207991644580082</v>
+        <v>16.5915362017711</v>
       </c>
       <c r="D2" t="n">
-        <v>16.06335593688631</v>
+        <v>19.15978819608075</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.28366833326509</v>
+        <v>8.197593330460867</v>
       </c>
       <c r="C3" t="n">
-        <v>29.00082718345078</v>
+        <v>29.1480893390878</v>
       </c>
       <c r="D3" t="n">
-        <v>41.51320167407638</v>
+        <v>52.22406912740908</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.75066144531709</v>
+        <v>22.25818395068368</v>
       </c>
       <c r="C4" t="n">
-        <v>59.37217416203011</v>
+        <v>88.54775243683682</v>
       </c>
       <c r="D4" t="n">
-        <v>42.47433267653401</v>
+        <v>57.18974901548945</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.08427573831176</v>
+        <v>33.89483948912113</v>
       </c>
       <c r="C5" t="n">
-        <v>83.47309855358506</v>
+        <v>179.8070920328034</v>
       </c>
       <c r="D5" t="n">
-        <v>33.4285093296039</v>
+        <v>41.65064635267094</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.69564251615027</v>
+        <v>29.46421209985528</v>
       </c>
       <c r="C6" t="n">
-        <v>83.44168262704918</v>
+        <v>226.0130477331795</v>
       </c>
       <c r="D6" t="n">
-        <v>32.6440929139107</v>
+        <v>37.71580155404972</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.77958979262998</v>
+        <v>15.63040519931347</v>
       </c>
       <c r="C7" t="n">
-        <v>53.29908286355933</v>
+        <v>144.4465032212417</v>
       </c>
       <c r="D7" t="n">
-        <v>33.29695513723482</v>
+        <v>38.20765715387736</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
-        <v>25.86905200690345</v>
+        <v>52.82293522699963</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>37.63529824230147</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.098436812331936</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>30.84062238120929</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>39.60468413702056</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>42.99073196896783</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>32.76190263842031</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>44.91201222617883</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>32.26022956155019</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>29.80684204863741</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>28.30869505195678</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.285352652791761</v>
+        <v>17.61642796519597</v>
       </c>
       <c r="C21" t="n">
-        <v>75.58553377271453</v>
+        <v>125.0766385528914</v>
       </c>
       <c r="D21" t="n">
-        <v>6.374683571192791</v>
+        <v>5.28492838955879</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.249985811684442</v>
+        <v>1.361684065790326</v>
       </c>
       <c r="C2" t="n">
-        <v>7.204064653763095</v>
+        <v>10.88365504928014</v>
       </c>
       <c r="D2" t="n">
-        <v>15.08848046656923</v>
+        <v>15.57542732787565</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.68971097219578</v>
+        <v>12.66945412330509</v>
       </c>
       <c r="C3" t="n">
-        <v>28.71121161069797</v>
+        <v>53.00455855228529</v>
       </c>
       <c r="D3" t="n">
-        <v>44.72842540548468</v>
+        <v>55.43929285881739</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.98788453684632</v>
+        <v>16.28523091804609</v>
       </c>
       <c r="C4" t="n">
-        <v>66.63416193034375</v>
+        <v>140.7600405917949</v>
       </c>
       <c r="D4" t="n">
-        <v>53.33540752861647</v>
+        <v>52.63345792008</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.53926689373454</v>
+        <v>16.5915362017711</v>
       </c>
       <c r="C5" t="n">
-        <v>98.81290643244149</v>
+        <v>135.0393967191488</v>
       </c>
       <c r="D5" t="n">
-        <v>41.67519004527711</v>
+        <v>34.11573272257667</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.27553661419064</v>
+        <v>9.700649065662736</v>
       </c>
       <c r="C6" t="n">
-        <v>111.1750735243173</v>
+        <v>95.11466283054375</v>
       </c>
       <c r="D6" t="n">
-        <v>36.22649028670731</v>
+        <v>25.15728492132452</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.04394196697963</v>
+        <v>5.809001166028376</v>
       </c>
       <c r="C7" t="n">
-        <v>90.72821408796898</v>
+        <v>37.12969817461437</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>26.40999499194344</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.92899537012474</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>50.23603002630928</v>
+        <v>22.69800692218626</v>
       </c>
       <c r="D8" t="n">
-        <v>34.46425315758427</v>
+        <v>29.12354564648163</v>
       </c>
     </row>
     <row r="9">
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>28.84374755077128</v>
+        <v>25.4046853427947</v>
       </c>
       <c r="D9" t="n">
         <v>32.72655972106742</v>
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>25.33890824661018</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6518,10 +6518,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>26.25291535926396</v>
       </c>
       <c r="D12" t="n">
         <v>33.62976760897449</v>
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>24.71549845441346</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>33.80157345721769</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>24.79894700927443</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>29.75873641112932</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>95.49459919208724</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.497512193325517</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>85.28420119907776</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.497512193325517</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
